--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5157,7 +5160,7 @@
         <v>3888.11</v>
       </c>
       <c r="F56" t="n">
-        <v>-42.01</v>
+        <v>-42</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>-0.0107</v>
@@ -5223,31 +5226,115 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3867.02</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3895.51</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3867.02</v>
+      </c>
+      <c r="E57" t="n">
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3745.95</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3773.54</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3835.07</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3896.59</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3941.15</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3985.71</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4064.2</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I57" s="13" t="n">
-        <v>3745.95</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>3773.54</v>
-      </c>
-      <c r="K57" s="13" t="n">
-        <v>3835.07</v>
-      </c>
-      <c r="L57" s="13" t="n">
-        <v>3896.59</v>
-      </c>
-      <c r="M57" s="13" t="n">
-        <v>3941.15</v>
-      </c>
-      <c r="N57" s="13" t="n">
-        <v>3985.71</v>
-      </c>
-      <c r="O57" s="13" t="n">
-        <v>4064.2</v>
+      <c r="I58" s="14" t="n">
+        <v>3838.53</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O58" s="14" t="n">
+        <v>3924</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -669,25 +666,25 @@
         <v>123.38</v>
       </c>
       <c r="I2" t="n">
-        <v>3554.48</v>
+        <v>3591.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3636.41</v>
+        <v>3650.16</v>
       </c>
       <c r="K2" t="n">
-        <v>3659.2</v>
+        <v>3668.37</v>
       </c>
       <c r="L2" t="n">
-        <v>3681.98</v>
+        <v>3686.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3734.34</v>
+        <v>3725.18</v>
       </c>
       <c r="N2" t="n">
-        <v>3786.7</v>
+        <v>3763.78</v>
       </c>
       <c r="O2" t="n">
-        <v>3779.92</v>
+        <v>3761.58</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5241,13 +5238,13 @@
         <v>3867.02</v>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>3885.33</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>-2.78</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v/>
+        <v>-0.0007</v>
       </c>
       <c r="H57" t="n">
         <v>28.49</v>
@@ -5273,10 +5270,8 @@
       <c r="O57" t="n">
         <v>4064.2</v>
       </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P57" s="6" t="n">
+        <v/>
       </c>
       <c r="Q57" s="6" t="n">
         <v/>
@@ -5284,9 +5279,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5305,35 +5300,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="14" t="n">
+      <c r="I58" s="13" t="n">
         <v>3838.53</v>
       </c>
-      <c r="J58" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K58" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="14" t="n">
+      <c r="J58" s="13" t="n">
+        <v>3858.88</v>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>3871.09</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>3883.3</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>3899.58</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>3915.86</v>
+      </c>
+      <c r="O58" s="13" t="n">
         <v>3924</v>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5235,19 +5235,19 @@
         <v>3895.51</v>
       </c>
       <c r="D57" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E57" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.78</v>
+        <v>-23.83</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0061</v>
       </c>
       <c r="H57" t="n">
-        <v>28.49</v>
+        <v>37.36</v>
       </c>
       <c r="I57" t="n">
         <v>3745.95</v>
@@ -5276,12 +5276,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5311,25 +5313,25 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>3838.53</v>
+        <v>3820.79</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>3858.88</v>
+        <v>3820.64</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>3871.09</v>
+        <v>3845.6</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>3883.3</v>
+        <v>3870.55</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3899.58</v>
+        <v>3882.96</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>3915.86</v>
+        <v>3895.36</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>3924</v>
+        <v>3932.87</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>123.38</v>
       </c>
       <c r="I2" t="n">
-        <v>3591.15</v>
+        <v>3611.98</v>
       </c>
       <c r="J2" t="n">
-        <v>3650.16</v>
+        <v>3657.97</v>
       </c>
       <c r="K2" t="n">
-        <v>3668.37</v>
+        <v>3673.57</v>
       </c>
       <c r="L2" t="n">
-        <v>3686.57</v>
+        <v>3689.17</v>
       </c>
       <c r="M2" t="n">
-        <v>3725.18</v>
+        <v>3719.97</v>
       </c>
       <c r="N2" t="n">
-        <v>3763.78</v>
+        <v>3750.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3761.58</v>
+        <v>3751.17</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -707,12 +707,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5235,19 +5235,19 @@
         <v>3895.51</v>
       </c>
       <c r="D57" t="n">
-        <v>3858.15</v>
+        <v>3867.02</v>
       </c>
       <c r="E57" t="n">
-        <v>3864.28</v>
+        <v>3885.33</v>
       </c>
       <c r="F57" t="n">
-        <v>-23.83</v>
+        <v>-2.78</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0007</v>
       </c>
       <c r="H57" t="n">
-        <v>37.36</v>
+        <v>28.49</v>
       </c>
       <c r="I57" t="n">
         <v>3745.95</v>
@@ -5276,14 +5276,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5313,25 +5311,25 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>3820.79</v>
+        <v>3838.53</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>3820.64</v>
+        <v>3858.88</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>3845.6</v>
+        <v>3871.09</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>3870.55</v>
+        <v>3883.3</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3882.96</v>
+        <v>3899.58</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>3895.36</v>
+        <v>3915.86</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>3932.87</v>
+        <v>3924</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5235,19 +5235,19 @@
         <v>3895.51</v>
       </c>
       <c r="D57" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E57" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F57" t="n">
-        <v>-23.83</v>
+        <v>3.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0061</v>
+        <v>0.0009</v>
       </c>
       <c r="H57" t="n">
-        <v>37.36</v>
+        <v>52.79</v>
       </c>
       <c r="I57" t="n">
         <v>3745.95</v>
@@ -5276,14 +5276,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5313,25 +5311,25 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>3820.79</v>
+        <v>3789.93</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>3820.64</v>
+        <v>3850.05</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>3845.6</v>
+        <v>3865.21</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>3870.55</v>
+        <v>3880.36</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3882.96</v>
+        <v>3917.99</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>3895.36</v>
+        <v>3955.63</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>3932.87</v>
+        <v>3948.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5232,22 +5232,22 @@
         <v>3867.02</v>
       </c>
       <c r="C57" t="n">
-        <v>3895.51</v>
+        <v>3898.84</v>
       </c>
       <c r="D57" t="n">
         <v>3842.72</v>
       </c>
       <c r="E57" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F57" t="n">
-        <v>3.49</v>
+        <v>-12.51</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0032</v>
       </c>
       <c r="H57" t="n">
-        <v>52.79</v>
+        <v>56.11</v>
       </c>
       <c r="I57" t="n">
         <v>3745.95</v>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5311,25 +5311,25 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>3789.93</v>
+        <v>3786.61</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>3850.05</v>
+        <v>3821.9</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>3865.21</v>
+        <v>3847.55</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>3880.36</v>
+        <v>3873.19</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3917.99</v>
+        <v>3903.66</v>
       </c>
       <c r="N58" s="13" t="n">
-        <v>3955.63</v>
+        <v>3934.13</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>3948.3</v>
+        <v>3954.95</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>123.38</v>
       </c>
       <c r="I2" t="n">
-        <v>3611.98</v>
+        <v>3614.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3657.97</v>
+        <v>3661.12</v>
       </c>
       <c r="K2" t="n">
-        <v>3673.57</v>
+        <v>3674.83</v>
       </c>
       <c r="L2" t="n">
-        <v>3689.17</v>
+        <v>3688.54</v>
       </c>
       <c r="M2" t="n">
-        <v>3719.97</v>
+        <v>3718.71</v>
       </c>
       <c r="N2" t="n">
-        <v>3750.76</v>
+        <v>3748.88</v>
       </c>
       <c r="O2" t="n">
-        <v>3751.17</v>
+        <v>3746.13</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -707,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5302,34 +5295,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I58" s="13" t="n">
-        <v>3786.61</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>3821.9</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>3847.55</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>3873.19</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>3903.66</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>3934.13</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>3954.95</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3712.5</v>
+        <v>3848.16</v>
       </c>
       <c r="C2" t="n">
-        <v>3825.76</v>
+        <v>3888.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3702.38</v>
+        <v>3761.42</v>
       </c>
       <c r="E2" t="n">
-        <v>3825.76</v>
+        <v>3857.93</v>
       </c>
       <c r="F2" t="n">
-        <v>128.99</v>
+        <v>32.17</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>123.38</v>
+        <v>127.18</v>
       </c>
       <c r="I2" t="n">
-        <v>3614.5</v>
+        <v>3579</v>
       </c>
       <c r="J2" t="n">
-        <v>3661.12</v>
+        <v>3733.22</v>
       </c>
       <c r="K2" t="n">
-        <v>3674.83</v>
+        <v>3764.07</v>
       </c>
       <c r="L2" t="n">
-        <v>3688.54</v>
+        <v>3794.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3718.71</v>
+        <v>3887.45</v>
       </c>
       <c r="N2" t="n">
-        <v>3748.88</v>
+        <v>3979.98</v>
       </c>
       <c r="O2" t="n">
-        <v>3746.13</v>
+        <v>3949.14</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,18 +697,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,72 +716,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3848.16</v>
+        <v>3869.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3888.6</v>
+        <v>3885.31</v>
       </c>
       <c r="D3" t="n">
-        <v>3761.42</v>
+        <v>3732.84</v>
       </c>
       <c r="E3" t="n">
-        <v>3857.93</v>
+        <v>3812.51</v>
       </c>
       <c r="F3" t="n">
-        <v>32.17</v>
+        <v>-45.41</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0118</v>
       </c>
       <c r="H3" t="n">
-        <v>127.18</v>
+        <v>152.47</v>
       </c>
       <c r="I3" t="n">
-        <v>3579</v>
+        <v>3634.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3733.22</v>
+        <v>3747.21</v>
       </c>
       <c r="K3" t="n">
-        <v>3764.07</v>
+        <v>3794.34</v>
       </c>
       <c r="L3" t="n">
-        <v>3794.91</v>
+        <v>3841.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3887.45</v>
+        <v>3921.51</v>
       </c>
       <c r="N3" t="n">
-        <v>3979.98</v>
+        <v>4001.56</v>
       </c>
       <c r="O3" t="n">
-        <v>3949.14</v>
+        <v>4015.77</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -795,77 +793,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3869.75</v>
+        <v>3811.67</v>
       </c>
       <c r="C4" t="n">
-        <v>3885.31</v>
+        <v>3892.74</v>
       </c>
       <c r="D4" t="n">
-        <v>3732.84</v>
+        <v>3791.72</v>
       </c>
       <c r="E4" t="n">
-        <v>3812.51</v>
+        <v>3870.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-45.41</v>
+        <v>58.08</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0118</v>
+        <v>0.0152</v>
       </c>
       <c r="H4" t="n">
-        <v>152.47</v>
+        <v>101.01</v>
       </c>
       <c r="I4" t="n">
-        <v>3634.25</v>
+        <v>3580.37</v>
       </c>
       <c r="J4" t="n">
-        <v>3747.21</v>
+        <v>3661.76</v>
       </c>
       <c r="K4" t="n">
-        <v>3794.34</v>
+        <v>3736.28</v>
       </c>
       <c r="L4" t="n">
-        <v>3841.47</v>
+        <v>3810.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3921.51</v>
+        <v>3888.75</v>
       </c>
       <c r="N4" t="n">
-        <v>4001.56</v>
+        <v>3966.71</v>
       </c>
       <c r="O4" t="n">
-        <v>4015.77</v>
+        <v>4037.79</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -877,59 +877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3811.67</v>
+        <v>3876.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3892.74</v>
+        <v>3899.96</v>
       </c>
       <c r="D5" t="n">
-        <v>3791.72</v>
+        <v>3801</v>
       </c>
       <c r="E5" t="n">
-        <v>3870.6</v>
+        <v>3820.09</v>
       </c>
       <c r="F5" t="n">
-        <v>58.08</v>
+        <v>-50.51</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0152</v>
+        <v>-0.013</v>
       </c>
       <c r="H5" t="n">
-        <v>101.01</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>3580.37</v>
+        <v>3690.71</v>
       </c>
       <c r="J5" t="n">
-        <v>3661.76</v>
+        <v>3783.77</v>
       </c>
       <c r="K5" t="n">
-        <v>3736.28</v>
+        <v>3820.09</v>
       </c>
       <c r="L5" t="n">
-        <v>3810.8</v>
+        <v>3856.41</v>
       </c>
       <c r="M5" t="n">
-        <v>3888.75</v>
+        <v>3921.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3966.71</v>
+        <v>3985.8</v>
       </c>
       <c r="O5" t="n">
-        <v>4037.79</v>
+        <v>3993.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,19 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,55 +957,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3876.1</v>
+        <v>3822.01</v>
       </c>
       <c r="C6" t="n">
-        <v>3899.96</v>
+        <v>3866.11</v>
       </c>
       <c r="D6" t="n">
-        <v>3801</v>
+        <v>3774.53</v>
       </c>
       <c r="E6" t="n">
-        <v>3820.09</v>
+        <v>3828.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-50.51</v>
+        <v>8.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0021</v>
       </c>
       <c r="H6" t="n">
-        <v>98.95999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="I6" t="n">
-        <v>3690.71</v>
+        <v>3702.03</v>
       </c>
       <c r="J6" t="n">
-        <v>3783.77</v>
+        <v>3705.93</v>
       </c>
       <c r="K6" t="n">
-        <v>3820.09</v>
+        <v>3770.61</v>
       </c>
       <c r="L6" t="n">
-        <v>3856.41</v>
+        <v>3835.28</v>
       </c>
       <c r="M6" t="n">
-        <v>3921.1</v>
+        <v>3869.57</v>
       </c>
       <c r="N6" t="n">
-        <v>3985.8</v>
+        <v>3903.86</v>
       </c>
       <c r="O6" t="n">
-        <v>3993.75</v>
+        <v>3998.92</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,14 +1017,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1043,57 +1041,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C7" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D7" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E7" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F7" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H7" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3702.03</v>
+        <v>3682.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3705.93</v>
+        <v>3740.42</v>
       </c>
       <c r="K7" t="n">
-        <v>3770.61</v>
+        <v>3782.32</v>
       </c>
       <c r="L7" t="n">
-        <v>3835.28</v>
+        <v>3824.21</v>
       </c>
       <c r="M7" t="n">
-        <v>3869.57</v>
+        <v>3873.89</v>
       </c>
       <c r="N7" t="n">
-        <v>3903.86</v>
+        <v>3923.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3998.92</v>
+        <v>3957.68</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,13 +1102,15 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1123,59 +1123,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C8" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D8" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E8" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F8" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H8" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I8" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L8" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M8" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N8" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1212,68 +1208,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C9" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D9" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F9" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H9" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I9" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J9" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K9" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L9" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M9" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N9" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>3987.41</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1287,84 +1289,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C10" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D10" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E10" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F10" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H10" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I10" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J10" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L10" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M10" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O10" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1373,59 +1375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C11" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D11" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E11" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F11" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H11" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I11" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J11" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L11" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M11" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N11" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O11" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,7 +1436,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1446,10 +1444,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1464,50 +1460,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C12" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D12" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E12" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F12" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H12" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I12" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J12" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K12" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L12" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M12" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N12" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O12" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,17 +1516,19 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1537,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C13" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D13" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E13" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F13" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H13" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I13" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J13" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K13" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L13" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M13" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N13" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O13" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,18 +1602,14 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1623,70 +1621,76 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C14" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D14" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E14" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H14" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I14" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J14" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K14" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L14" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M14" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N14" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O14" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4087.48</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1698,83 +1702,73 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C15" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D15" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E15" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H15" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J15" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K15" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L15" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M15" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N15" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O15" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4150.06</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1791,55 +1785,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C16" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D16" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E16" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F16" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H16" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I16" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J16" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K16" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L16" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O16" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,11 +1850,13 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1871,75 +1871,79 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C17" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D17" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F17" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H17" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J17" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K17" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L17" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N17" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1955,80 +1959,76 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C18" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D18" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E18" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I18" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J18" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K18" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L18" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2050,50 +2050,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C19" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D19" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E19" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H19" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I19" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J19" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K19" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L19" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N19" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O19" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,24 +2101,26 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
@@ -2127,57 +2129,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C20" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D20" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E20" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F20" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H20" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I20" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J20" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K20" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L20" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N20" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,21 +2192,17 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
@@ -2220,50 +2218,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C21" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D21" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E21" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F21" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H21" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J21" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K21" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L21" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M21" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N21" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,76 +2274,78 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C22" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D22" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E22" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F22" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H22" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I22" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J22" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K22" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L22" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M22" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O22" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2366,70 +2366,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C23" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D23" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E23" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I23" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J23" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K23" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L23" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M23" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N23" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O23" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,10 +2445,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2463,74 +2461,80 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C24" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D24" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E24" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F24" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H24" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I24" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J24" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K24" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L24" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M24" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N24" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O24" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2552,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C25" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D25" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E25" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H25" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I25" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J25" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K25" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L25" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M25" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N25" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O25" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,18 +2611,16 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2633,79 +2635,77 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C26" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D26" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E26" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F26" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H26" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I26" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J26" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K26" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L26" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M26" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O26" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2717,59 +2717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C27" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D27" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E27" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F27" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H27" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I27" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J27" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K27" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L27" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N27" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O27" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2782,7 +2778,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2790,8 +2786,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2806,63 +2804,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C28" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D28" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E28" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F28" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I28" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J28" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K28" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L28" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M28" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N28" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O28" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2870,10 +2872,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2883,78 +2883,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D29" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E29" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F29" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H29" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K29" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L29" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M29" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O29" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2969,63 +2969,67 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C30" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D30" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E30" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F30" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H30" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I30" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J30" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K30" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L30" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M30" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N30" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O30" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3034,7 +3038,7 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3046,78 +3050,72 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C31" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D31" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E31" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F31" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H31" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I31" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J31" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K31" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L31" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M31" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N31" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O31" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
@@ -3144,67 +3142,63 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C32" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D32" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E32" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H32" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I32" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J32" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K32" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L32" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M32" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N32" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O32" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
       </c>
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3221,55 +3215,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C33" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D33" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E33" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F33" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H33" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I33" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J33" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K33" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L33" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M33" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N33" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O33" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,78 +3278,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C34" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D34" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E34" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F34" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H34" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I34" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J34" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K34" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L34" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M34" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O34" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,13 +3367,11 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3390,50 +3386,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C35" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D35" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E35" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F35" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H35" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I35" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J35" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K35" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L35" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M35" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N35" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O35" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3470,50 +3466,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C36" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D36" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E36" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F36" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I36" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J36" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K36" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L36" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M36" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N36" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O36" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3550,50 +3546,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C37" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D37" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E37" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F37" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H37" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I37" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J37" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K37" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L37" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M37" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N37" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O37" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,14 +3607,18 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3630,63 +3630,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C38" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D38" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E38" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F38" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H38" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I38" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J38" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K38" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L38" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M38" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N38" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O38" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3696,7 +3700,7 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
@@ -3704,152 +3708,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C39" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D39" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E39" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F39" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H39" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I39" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J39" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K39" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L39" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M39" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N39" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O39" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C40" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D40" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E40" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F40" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H40" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I40" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J40" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K40" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L40" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M40" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N40" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O40" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,12 +3851,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3884,50 +3880,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C41" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D41" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E41" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F41" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I41" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J41" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K41" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L41" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M41" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N41" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O41" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3964,50 +3960,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C42" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D42" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E42" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H42" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I42" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J42" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K42" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L42" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M42" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N42" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O42" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4017,12 +4013,12 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4039,55 +4035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C43" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D43" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E43" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F43" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H43" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I43" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J43" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K43" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L43" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M43" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N43" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O43" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4095,18 +4095,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4121,79 +4121,85 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C44" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D44" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E44" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F44" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H44" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I44" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J44" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K44" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L44" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M44" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N44" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O44" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4205,85 +4211,79 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C45" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D45" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E45" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F45" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H45" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I45" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J45" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K45" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L45" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N45" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O45" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4302,50 +4302,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C46" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D46" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E46" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F46" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H46" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I46" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J46" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K46" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L46" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M46" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N46" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O46" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4353,18 +4353,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4377,69 +4377,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C47" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D47" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E47" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F47" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H47" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I47" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J47" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K47" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L47" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M47" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N47" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O47" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4466,74 +4466,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C48" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D48" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E48" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H48" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I48" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J48" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K48" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L48" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M48" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N48" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O48" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4545,55 +4541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C49" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D49" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E49" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F49" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H49" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I49" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J49" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K49" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L49" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M49" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N49" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O49" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4609,10 +4609,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4627,57 +4625,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C50" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D50" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E50" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F50" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H50" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I50" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J50" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K50" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L50" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M50" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N50" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O50" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4690,76 +4688,76 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C51" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D51" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E51" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F51" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H51" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I51" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J51" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K51" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L51" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M51" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N51" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O51" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4772,18 +4770,14 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4793,55 +4787,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C52" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D52" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E52" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F52" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H52" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I52" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J52" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K52" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L52" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M52" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N52" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O52" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4849,19 +4847,25 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4873,57 +4877,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C53" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D53" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E53" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F53" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H53" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I53" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J53" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K53" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L53" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M53" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N53" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O53" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4931,25 +4935,21 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4968,50 +4968,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C54" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D54" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E54" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F54" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H54" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I54" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J54" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K54" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L54" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M54" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N54" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O54" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5022,15 +5022,13 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5045,57 +5043,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C55" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D55" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E55" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F55" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H55" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I55" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J55" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K55" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L55" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M55" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N55" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O55" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,12 +5101,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5127,57 +5127,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C56" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D56" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E56" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F56" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H56" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I56" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J56" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K56" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L56" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M56" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N56" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O56" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5185,14 +5185,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5211,89 +5209,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3867.02</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3898.84</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3842.72</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3875.6</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-12.51</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0032</v>
-      </c>
-      <c r="H57" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3745.95</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3773.54</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3835.07</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3896.59</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3941.15</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3985.71</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4064.2</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5213,6 +5216,88 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3920.27</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3950.94</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3918.13</v>
+      </c>
+      <c r="E57" t="n">
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3765.77</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3850.26</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3873.4</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3896.53</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3950.35</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4004.16</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3996.62</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>127.18</v>
       </c>
       <c r="I2" t="n">
-        <v>3579</v>
+        <v>3584.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3733.22</v>
+        <v>3735.18</v>
       </c>
       <c r="K2" t="n">
-        <v>3764.07</v>
+        <v>3765.38</v>
       </c>
       <c r="L2" t="n">
-        <v>3794.91</v>
+        <v>3795.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3887.45</v>
+        <v>3886.14</v>
       </c>
       <c r="N2" t="n">
-        <v>3979.98</v>
+        <v>3976.72</v>
       </c>
       <c r="O2" t="n">
-        <v>3949.14</v>
+        <v>3946.53</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5232,13 +5229,13 @@
         <v>3918.13</v>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>3949.91</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>38.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v/>
+        <v>0.0097</v>
       </c>
       <c r="H57" t="n">
         <v>32.81</v>
@@ -5264,25 +5261,23 @@
       <c r="O57" t="n">
         <v>3996.62</v>
       </c>
-      <c r="P57" s="6" t="inlineStr">
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5223,22 +5223,22 @@
         <v>3920.27</v>
       </c>
       <c r="C57" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D57" t="n">
         <v>3918.13</v>
       </c>
       <c r="E57" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F57" t="n">
-        <v>38.04</v>
+        <v>40.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0103</v>
       </c>
       <c r="H57" t="n">
-        <v>32.81</v>
+        <v>49.55</v>
       </c>
       <c r="I57" t="n">
         <v>3765.77</v>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5223,22 +5223,22 @@
         <v>3920.27</v>
       </c>
       <c r="C57" t="n">
-        <v>3967.68</v>
+        <v>3950.94</v>
       </c>
       <c r="D57" t="n">
         <v>3918.13</v>
       </c>
       <c r="E57" t="n">
-        <v>3952.13</v>
+        <v>3949.91</v>
       </c>
       <c r="F57" t="n">
-        <v>40.26</v>
+        <v>38.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.0097</v>
       </c>
       <c r="H57" t="n">
-        <v>49.55</v>
+        <v>32.81</v>
       </c>
       <c r="I57" t="n">
         <v>3765.77</v>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5223,22 +5223,22 @@
         <v>3920.27</v>
       </c>
       <c r="C57" t="n">
-        <v>3950.94</v>
+        <v>3951.52</v>
       </c>
       <c r="D57" t="n">
         <v>3918.13</v>
       </c>
       <c r="E57" t="n">
-        <v>3949.91</v>
+        <v>3936.52</v>
       </c>
       <c r="F57" t="n">
-        <v>38.04</v>
+        <v>24.65</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0063</v>
       </c>
       <c r="H57" t="n">
-        <v>32.81</v>
+        <v>33.4</v>
       </c>
       <c r="I57" t="n">
         <v>3765.77</v>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>127.18</v>
       </c>
       <c r="I2" t="n">
-        <v>3584.22</v>
+        <v>3690.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3735.18</v>
+        <v>3774.93</v>
       </c>
       <c r="K2" t="n">
-        <v>3765.38</v>
+        <v>3791.88</v>
       </c>
       <c r="L2" t="n">
-        <v>3795.57</v>
+        <v>3808.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3886.14</v>
+        <v>3859.64</v>
       </c>
       <c r="N2" t="n">
-        <v>3976.72</v>
+        <v>3910.47</v>
       </c>
       <c r="O2" t="n">
-        <v>3946.53</v>
+        <v>3893.53</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5226,19 +5228,19 @@
         <v>3951.52</v>
       </c>
       <c r="D57" t="n">
-        <v>3918.13</v>
+        <v>3888.37</v>
       </c>
       <c r="E57" t="n">
-        <v>3936.52</v>
+        <v>3888.37</v>
       </c>
       <c r="F57" t="n">
-        <v>24.65</v>
+        <v>-23.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0063</v>
+        <v>-0.006</v>
       </c>
       <c r="H57" t="n">
-        <v>33.4</v>
+        <v>63.15</v>
       </c>
       <c r="I57" t="n">
         <v>3765.77</v>
@@ -5270,14 +5272,14 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5291,7 +5293,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3848.16</v>
+        <v>3869.75</v>
       </c>
       <c r="C2" t="n">
-        <v>3888.6</v>
+        <v>3885.31</v>
       </c>
       <c r="D2" t="n">
-        <v>3761.42</v>
+        <v>3732.84</v>
       </c>
       <c r="E2" t="n">
-        <v>3857.93</v>
+        <v>3812.51</v>
       </c>
       <c r="F2" t="n">
-        <v>32.17</v>
+        <v>-45.41</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0118</v>
       </c>
       <c r="H2" t="n">
-        <v>127.18</v>
+        <v>152.47</v>
       </c>
       <c r="I2" t="n">
-        <v>3690.22</v>
+        <v>3634.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3774.93</v>
+        <v>3747.21</v>
       </c>
       <c r="K2" t="n">
-        <v>3791.88</v>
+        <v>3794.34</v>
       </c>
       <c r="L2" t="n">
-        <v>3808.82</v>
+        <v>3841.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3859.64</v>
+        <v>3921.51</v>
       </c>
       <c r="N2" t="n">
-        <v>3910.47</v>
+        <v>4001.56</v>
       </c>
       <c r="O2" t="n">
-        <v>3893.53</v>
+        <v>4015.77</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -689,18 +689,16 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,77 +711,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3869.75</v>
+        <v>3811.67</v>
       </c>
       <c r="C3" t="n">
-        <v>3885.31</v>
+        <v>3892.74</v>
       </c>
       <c r="D3" t="n">
-        <v>3732.84</v>
+        <v>3791.72</v>
       </c>
       <c r="E3" t="n">
-        <v>3812.51</v>
+        <v>3870.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-45.41</v>
+        <v>58.08</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0118</v>
+        <v>0.0152</v>
       </c>
       <c r="H3" t="n">
-        <v>152.47</v>
+        <v>101.01</v>
       </c>
       <c r="I3" t="n">
-        <v>3634.25</v>
+        <v>3580.37</v>
       </c>
       <c r="J3" t="n">
-        <v>3747.21</v>
+        <v>3661.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3794.34</v>
+        <v>3736.28</v>
       </c>
       <c r="L3" t="n">
-        <v>3841.47</v>
+        <v>3810.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3921.51</v>
+        <v>3888.75</v>
       </c>
       <c r="N3" t="n">
-        <v>4001.56</v>
+        <v>3966.71</v>
       </c>
       <c r="O3" t="n">
-        <v>4015.77</v>
+        <v>4037.79</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -795,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3811.67</v>
+        <v>3876.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3892.74</v>
+        <v>3899.96</v>
       </c>
       <c r="D4" t="n">
-        <v>3791.72</v>
+        <v>3801</v>
       </c>
       <c r="E4" t="n">
-        <v>3870.6</v>
+        <v>3820.09</v>
       </c>
       <c r="F4" t="n">
-        <v>58.08</v>
+        <v>-50.51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0152</v>
+        <v>-0.013</v>
       </c>
       <c r="H4" t="n">
-        <v>101.01</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3580.37</v>
+        <v>3690.71</v>
       </c>
       <c r="J4" t="n">
-        <v>3661.76</v>
+        <v>3783.77</v>
       </c>
       <c r="K4" t="n">
-        <v>3736.28</v>
+        <v>3820.09</v>
       </c>
       <c r="L4" t="n">
-        <v>3810.8</v>
+        <v>3856.41</v>
       </c>
       <c r="M4" t="n">
-        <v>3888.75</v>
+        <v>3921.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3966.71</v>
+        <v>3985.8</v>
       </c>
       <c r="O4" t="n">
-        <v>4037.79</v>
+        <v>3993.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,18 +851,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -879,55 +875,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3876.1</v>
+        <v>3822.01</v>
       </c>
       <c r="C5" t="n">
-        <v>3899.96</v>
+        <v>3866.11</v>
       </c>
       <c r="D5" t="n">
-        <v>3801</v>
+        <v>3774.53</v>
       </c>
       <c r="E5" t="n">
-        <v>3820.09</v>
+        <v>3828.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-50.51</v>
+        <v>8.02</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0021</v>
       </c>
       <c r="H5" t="n">
-        <v>98.95999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="I5" t="n">
-        <v>3690.71</v>
+        <v>3702.03</v>
       </c>
       <c r="J5" t="n">
-        <v>3783.77</v>
+        <v>3705.93</v>
       </c>
       <c r="K5" t="n">
-        <v>3820.09</v>
+        <v>3770.61</v>
       </c>
       <c r="L5" t="n">
-        <v>3856.41</v>
+        <v>3835.28</v>
       </c>
       <c r="M5" t="n">
-        <v>3921.1</v>
+        <v>3869.57</v>
       </c>
       <c r="N5" t="n">
-        <v>3985.8</v>
+        <v>3903.86</v>
       </c>
       <c r="O5" t="n">
-        <v>3993.75</v>
+        <v>3998.92</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,14 +935,12 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C6" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D6" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E6" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F6" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H6" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3702.03</v>
+        <v>3682.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3705.93</v>
+        <v>3740.42</v>
       </c>
       <c r="K6" t="n">
-        <v>3770.61</v>
+        <v>3782.32</v>
       </c>
       <c r="L6" t="n">
-        <v>3835.28</v>
+        <v>3824.21</v>
       </c>
       <c r="M6" t="n">
-        <v>3869.57</v>
+        <v>3873.89</v>
       </c>
       <c r="N6" t="n">
-        <v>3903.86</v>
+        <v>3923.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3998.92</v>
+        <v>3957.68</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,11 +1022,13 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1041,59 +1041,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C7" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D7" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E7" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F7" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H7" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I7" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K7" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L7" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M7" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N7" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,7 +1100,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1130,68 +1126,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D8" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E8" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F8" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H8" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I8" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J8" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K8" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L8" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M8" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N8" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>3987.41</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1205,84 +1207,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C9" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D9" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E9" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F9" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H9" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I9" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J9" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L9" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N9" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1291,59 +1293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C10" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D10" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E10" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F10" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H10" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I10" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J10" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L10" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N10" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O10" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,9 +1352,9 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1364,10 +1362,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1382,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C11" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D11" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E11" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F11" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H11" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I11" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L11" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M11" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N11" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,19 +1432,21 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1457,55 +1455,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C12" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D12" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E12" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F12" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J12" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K12" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L12" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M12" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N12" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O12" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,20 +1518,16 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1541,70 +1539,76 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C13" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D13" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E13" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H13" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I13" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J13" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L13" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M13" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N13" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O13" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>4087.48</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1616,83 +1620,73 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C14" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D14" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E14" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H14" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J14" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K14" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L14" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M14" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4150.06</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1709,55 +1703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C15" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D15" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E15" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F15" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H15" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I15" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J15" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K15" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L15" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O15" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,13 +1766,15 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1789,75 +1789,79 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C16" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D16" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E16" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F16" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H16" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J16" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K16" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L16" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M16" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N16" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O16" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1873,80 +1877,76 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C17" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D17" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E17" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I17" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J17" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K17" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L17" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O17" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1968,50 +1968,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C18" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D18" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E18" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H18" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I18" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J18" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K18" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L18" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N18" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O18" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2019,24 +2019,26 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
@@ -2045,57 +2047,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C19" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D19" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E19" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F19" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H19" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I19" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J19" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K19" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L19" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N19" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O19" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,23 +2108,19 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
@@ -2138,50 +2136,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C20" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D20" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E20" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F20" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H20" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J20" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K20" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L20" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M20" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N20" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O20" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,78 +2190,80 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C21" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D21" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E21" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F21" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H21" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I21" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J21" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K21" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L21" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N21" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,9 +2274,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2284,70 +2284,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C22" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D22" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E22" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I22" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J22" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K22" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L22" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M22" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N22" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O22" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,15 +2358,13 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2381,74 +2379,80 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C23" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D23" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E23" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F23" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H23" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I23" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J23" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K23" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L23" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M23" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N23" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O23" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2470,50 +2474,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C24" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D24" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E24" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H24" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I24" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J24" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K24" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L24" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M24" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N24" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O24" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,18 +2529,16 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2551,79 +2553,77 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C25" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D25" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E25" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F25" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H25" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I25" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J25" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K25" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L25" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M25" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O25" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2635,59 +2635,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C26" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D26" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E26" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F26" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H26" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I26" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J26" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K26" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L26" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M26" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N26" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O26" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2698,9 +2694,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2708,8 +2704,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2724,63 +2722,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C27" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D27" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E27" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F27" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I27" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J27" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K27" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L27" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M27" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N27" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O27" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2788,10 +2790,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2801,78 +2801,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C28" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D28" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E28" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F28" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H28" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K28" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L28" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M28" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O28" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2887,72 +2887,76 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C29" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D29" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E29" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F29" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H29" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I29" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J29" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K29" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L29" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M29" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N29" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O29" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2964,81 +2968,75 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C30" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D30" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E30" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F30" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H30" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I30" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J30" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K30" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L30" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M30" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O30" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3062,67 +3060,63 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C31" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D31" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E31" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H31" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I31" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J31" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K31" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L31" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M31" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N31" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O31" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
       </c>
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3139,55 +3133,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C32" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D32" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E32" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F32" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H32" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I32" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J32" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K32" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L32" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M32" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N32" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O32" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3200,76 +3198,76 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C33" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D33" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E33" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F33" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H33" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I33" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J33" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K33" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L33" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M33" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N33" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O33" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,20 +3278,18 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3308,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C34" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D34" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E34" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F34" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I34" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J34" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K34" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L34" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M34" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N34" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O34" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,7 +3358,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3388,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C35" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D35" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E35" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F35" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I35" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J35" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K35" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L35" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M35" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N35" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O35" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3442,7 +3438,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3468,50 +3464,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C36" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D36" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E36" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F36" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H36" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I36" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J36" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K36" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L36" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M36" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N36" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O36" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3522,21 +3518,25 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3548,63 +3548,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C37" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D37" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E37" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F37" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H37" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I37" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J37" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K37" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L37" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M37" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N37" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O37" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3614,7 +3618,7 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
@@ -3622,152 +3626,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C38" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D38" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E38" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F38" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H38" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I38" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J38" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K38" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L38" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M38" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N38" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O38" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C39" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D39" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E39" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F39" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H39" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I39" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J39" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K39" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L39" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M39" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N39" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O39" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,12 +3769,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3802,50 +3798,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C40" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D40" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E40" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F40" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I40" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J40" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K40" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L40" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M40" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N40" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O40" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3858,7 +3854,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3882,50 +3878,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C41" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D41" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E41" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H41" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I41" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J41" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K41" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L41" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M41" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N41" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O41" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3935,12 +3931,12 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3957,55 +3953,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C42" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D42" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E42" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F42" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H42" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I42" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J42" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K42" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L42" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M42" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N42" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O42" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4013,18 +4013,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4039,79 +4039,85 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C43" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D43" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E43" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F43" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H43" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I43" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J43" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K43" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L43" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M43" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N43" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O43" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4123,85 +4129,79 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C44" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D44" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E44" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F44" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H44" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I44" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J44" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K44" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L44" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M44" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N44" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O44" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4220,50 +4220,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C45" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D45" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E45" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F45" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H45" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I45" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J45" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K45" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L45" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M45" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N45" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O45" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,18 +4271,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,72 +4295,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C46" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D46" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E46" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F46" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H46" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I46" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J46" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K46" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L46" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M46" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N46" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O46" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4384,74 +4384,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C47" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D47" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E47" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F47" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H47" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I47" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K47" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L47" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M47" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N47" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O47" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4463,55 +4459,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C48" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D48" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E48" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F48" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H48" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I48" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J48" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K48" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L48" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M48" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N48" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O48" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,15 +4522,13 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4545,57 +4543,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C49" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D49" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E49" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F49" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H49" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I49" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J49" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K49" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L49" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M49" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N49" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O49" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,78 +4604,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C50" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D50" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E50" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F50" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H50" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I50" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J50" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K50" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L50" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M50" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N50" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O50" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4688,20 +4686,16 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4711,55 +4705,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C51" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D51" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E51" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F51" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H51" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I51" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J51" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K51" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L51" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M51" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N51" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O51" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4767,19 +4765,25 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4791,57 +4795,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C52" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D52" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E52" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F52" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H52" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I52" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J52" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K52" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L52" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M52" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N52" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O52" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4849,25 +4853,21 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4886,50 +4886,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C53" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D53" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E53" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F53" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H53" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I53" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J53" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K53" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L53" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M53" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N53" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O53" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4942,13 +4942,11 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4963,57 +4961,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C54" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D54" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E54" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F54" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H54" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I54" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J54" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K54" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L54" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M54" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N54" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O54" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5021,12 +5019,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5045,57 +5045,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C55" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D55" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E55" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F55" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H55" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I55" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J55" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K55" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L55" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M55" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N55" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O55" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,14 +5103,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5129,57 +5127,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C56" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D56" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E56" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F56" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H56" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I56" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J56" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K56" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L56" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M56" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N56" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O56" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5192,11 +5190,13 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5210,90 +5210,6 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3920.27</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3951.52</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3888.37</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3888.37</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="H57" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3765.77</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3850.26</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3873.4</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3896.53</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3950.35</v>
-      </c>
-      <c r="N57" t="n">
-        <v>4004.16</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5215,6 +5218,92 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3878.41</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3878.41</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3806.67</v>
+      </c>
+      <c r="E57" t="n">
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>71.73999999999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3809.07</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3789.24</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3848.72</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3908.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3928.03</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3947.85</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4046.99</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5234,13 +5231,13 @@
         <v>3806.67</v>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>3830.45</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>-57.92</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v/>
+        <v>-0.0149</v>
       </c>
       <c r="H57" t="n">
         <v>71.73999999999999</v>
@@ -5268,20 +5265,20 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5300,7 +5297,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>152.47</v>
       </c>
       <c r="I2" t="n">
-        <v>3634.25</v>
+        <v>3635.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3747.21</v>
+        <v>3748.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3794.34</v>
+        <v>3795.04</v>
       </c>
       <c r="L2" t="n">
-        <v>3841.47</v>
+        <v>3841.12</v>
       </c>
       <c r="M2" t="n">
-        <v>3921.51</v>
+        <v>3920.81</v>
       </c>
       <c r="N2" t="n">
-        <v>4001.56</v>
+        <v>4000.51</v>
       </c>
       <c r="O2" t="n">
-        <v>4015.77</v>
+        <v>4012.97</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5231,13 +5231,13 @@
         <v>3806.67</v>
       </c>
       <c r="E57" t="n">
-        <v>3830.45</v>
+        <v>3842.19</v>
       </c>
       <c r="F57" t="n">
-        <v>-57.92</v>
+        <v>-46.18</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0119</v>
       </c>
       <c r="H57" t="n">
         <v>71.73999999999999</v>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>152.47</v>
       </c>
       <c r="I2" t="n">
-        <v>3635.65</v>
+        <v>3655.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3748.96</v>
+        <v>3773.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3795.04</v>
+        <v>3804.84</v>
       </c>
       <c r="L2" t="n">
-        <v>3841.12</v>
+        <v>3836.22</v>
       </c>
       <c r="M2" t="n">
-        <v>3920.81</v>
+        <v>3911.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4000.51</v>
+        <v>3985.82</v>
       </c>
       <c r="O2" t="n">
-        <v>4012.97</v>
+        <v>3973.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -713,7 +713,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3869.75</v>
+        <v>3811.67</v>
       </c>
       <c r="C2" t="n">
-        <v>3885.31</v>
+        <v>3892.74</v>
       </c>
       <c r="D2" t="n">
-        <v>3732.84</v>
+        <v>3791.72</v>
       </c>
       <c r="E2" t="n">
-        <v>3812.51</v>
+        <v>3870.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-45.41</v>
+        <v>58.08</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0118</v>
+        <v>0.0152</v>
       </c>
       <c r="H2" t="n">
-        <v>152.47</v>
+        <v>101.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3655.24</v>
+        <v>3580.37</v>
       </c>
       <c r="J2" t="n">
-        <v>3773.45</v>
+        <v>3661.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3804.84</v>
+        <v>3736.28</v>
       </c>
       <c r="L2" t="n">
-        <v>3836.22</v>
+        <v>3810.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3911.02</v>
+        <v>3888.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3985.82</v>
+        <v>3966.71</v>
       </c>
       <c r="O2" t="n">
-        <v>3973.79</v>
+        <v>4037.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3811.67</v>
+        <v>3876.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3892.74</v>
+        <v>3899.96</v>
       </c>
       <c r="D3" t="n">
-        <v>3791.72</v>
+        <v>3801</v>
       </c>
       <c r="E3" t="n">
-        <v>3870.6</v>
+        <v>3820.09</v>
       </c>
       <c r="F3" t="n">
-        <v>58.08</v>
+        <v>-50.51</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0152</v>
+        <v>-0.013</v>
       </c>
       <c r="H3" t="n">
-        <v>101.01</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3580.37</v>
+        <v>3690.71</v>
       </c>
       <c r="J3" t="n">
-        <v>3661.76</v>
+        <v>3783.77</v>
       </c>
       <c r="K3" t="n">
-        <v>3736.28</v>
+        <v>3820.09</v>
       </c>
       <c r="L3" t="n">
-        <v>3810.8</v>
+        <v>3856.41</v>
       </c>
       <c r="M3" t="n">
-        <v>3888.75</v>
+        <v>3921.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3966.71</v>
+        <v>3985.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4037.79</v>
+        <v>3993.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -795,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3876.1</v>
+        <v>3822.01</v>
       </c>
       <c r="C4" t="n">
-        <v>3899.96</v>
+        <v>3866.11</v>
       </c>
       <c r="D4" t="n">
-        <v>3801</v>
+        <v>3774.53</v>
       </c>
       <c r="E4" t="n">
-        <v>3820.09</v>
+        <v>3828.11</v>
       </c>
       <c r="F4" t="n">
-        <v>-50.51</v>
+        <v>8.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0021</v>
       </c>
       <c r="H4" t="n">
-        <v>98.95999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="I4" t="n">
-        <v>3690.71</v>
+        <v>3702.03</v>
       </c>
       <c r="J4" t="n">
-        <v>3783.77</v>
+        <v>3705.93</v>
       </c>
       <c r="K4" t="n">
-        <v>3820.09</v>
+        <v>3770.61</v>
       </c>
       <c r="L4" t="n">
-        <v>3856.41</v>
+        <v>3835.28</v>
       </c>
       <c r="M4" t="n">
-        <v>3921.1</v>
+        <v>3869.57</v>
       </c>
       <c r="N4" t="n">
-        <v>3985.8</v>
+        <v>3903.86</v>
       </c>
       <c r="O4" t="n">
-        <v>3993.75</v>
+        <v>3998.92</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,14 +849,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -877,57 +873,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C5" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D5" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E5" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F5" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H5" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3702.03</v>
+        <v>3682.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3705.93</v>
+        <v>3740.42</v>
       </c>
       <c r="K5" t="n">
-        <v>3770.61</v>
+        <v>3782.32</v>
       </c>
       <c r="L5" t="n">
-        <v>3835.28</v>
+        <v>3824.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3869.57</v>
+        <v>3873.89</v>
       </c>
       <c r="N5" t="n">
-        <v>3903.86</v>
+        <v>3923.58</v>
       </c>
       <c r="O5" t="n">
-        <v>3998.92</v>
+        <v>3957.68</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,11 +936,13 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -957,59 +955,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C6" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D6" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E6" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F6" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H6" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I6" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L6" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M6" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N6" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O6" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,7 +1014,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1046,68 +1040,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D7" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E7" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F7" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H7" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I7" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J7" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K7" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L7" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M7" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N7" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>3987.41</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1121,84 +1121,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C8" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D8" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E8" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H8" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I8" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J8" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L8" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M8" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N8" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1207,59 +1207,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C9" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D9" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E9" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F9" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H9" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I9" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J9" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L9" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N9" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O9" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,9 +1266,9 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -1280,10 +1276,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1298,50 +1292,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C10" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D10" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E10" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F10" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H10" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I10" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J10" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K10" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L10" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M10" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N10" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O10" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,19 +1346,21 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1373,55 +1369,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C11" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D11" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E11" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F11" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H11" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J11" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K11" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L11" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N11" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O11" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,20 +1432,16 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1457,70 +1453,76 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C12" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E12" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H12" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J12" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L12" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M12" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N12" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O12" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>4087.48</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1532,83 +1534,73 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C13" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D13" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E13" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F13" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H13" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J13" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K13" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L13" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M13" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N13" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O13" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4150.06</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1625,55 +1617,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C14" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D14" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E14" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F14" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H14" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I14" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J14" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K14" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L14" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M14" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O14" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,13 +1680,15 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1705,75 +1703,79 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C15" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D15" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E15" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F15" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H15" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J15" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K15" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L15" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N15" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1789,80 +1791,76 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C16" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D16" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E16" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I16" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J16" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K16" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L16" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1884,50 +1882,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C17" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D17" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E17" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H17" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I17" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J17" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K17" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L17" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N17" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O17" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,24 +1933,26 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1961,57 +1961,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C18" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D18" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E18" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F18" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H18" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I18" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J18" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K18" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L18" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M18" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N18" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,23 +2022,19 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
@@ -2054,50 +2050,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C19" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D19" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E19" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F19" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H19" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I19" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J19" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K19" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L19" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M19" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N19" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O19" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,78 +2104,80 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C20" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D20" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E20" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F20" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H20" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I20" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J20" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K20" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L20" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M20" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N20" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O20" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,9 +2188,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2200,70 +2198,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C21" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D21" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E21" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I21" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J21" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K21" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L21" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M21" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N21" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O21" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,15 +2272,13 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,74 +2293,80 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C22" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D22" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E22" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F22" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H22" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I22" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J22" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K22" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L22" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M22" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N22" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O22" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2386,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C23" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D23" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E23" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H23" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I23" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J23" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K23" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L23" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M23" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N23" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O23" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,18 +2443,16 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2467,79 +2467,77 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C24" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D24" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E24" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F24" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H24" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I24" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J24" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K24" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L24" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M24" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O24" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2551,59 +2549,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C25" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D25" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E25" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F25" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H25" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I25" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K25" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L25" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M25" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N25" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O25" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,9 +2608,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2624,8 +2618,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2640,63 +2636,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C26" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D26" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E26" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F26" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I26" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J26" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K26" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L26" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M26" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N26" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O26" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2704,10 +2704,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2717,78 +2715,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C27" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D27" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E27" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F27" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H27" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J27" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K27" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L27" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M27" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N27" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O27" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2803,72 +2801,76 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C28" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D28" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E28" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F28" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H28" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I28" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J28" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K28" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L28" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M28" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N28" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O28" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2880,81 +2882,75 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C29" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D29" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E29" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F29" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H29" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I29" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J29" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K29" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L29" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M29" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O29" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2978,67 +2974,63 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C30" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D30" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E30" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H30" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I30" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J30" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K30" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L30" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M30" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N30" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O30" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
       </c>
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3055,55 +3047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C31" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D31" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E31" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F31" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H31" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I31" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K31" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L31" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M31" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N31" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O31" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3116,76 +3112,76 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C32" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D32" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E32" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F32" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H32" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I32" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J32" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K32" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L32" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M32" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N32" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O32" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,20 +3192,18 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3224,50 +3218,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C33" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D33" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E33" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F33" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H33" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I33" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J33" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K33" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L33" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M33" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N33" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O33" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3278,7 +3272,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3304,50 +3298,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C34" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D34" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E34" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F34" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I34" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J34" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K34" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L34" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M34" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N34" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O34" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3358,7 +3352,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3384,50 +3378,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C35" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D35" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E35" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F35" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H35" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I35" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J35" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K35" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L35" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M35" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N35" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O35" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3438,21 +3432,25 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3464,63 +3462,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C36" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D36" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E36" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F36" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H36" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I36" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J36" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K36" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L36" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M36" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N36" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O36" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3530,7 +3532,7 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V36" s="8" t="inlineStr">
@@ -3538,152 +3540,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C37" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D37" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E37" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F37" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H37" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I37" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J37" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K37" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L37" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M37" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N37" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O37" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C38" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D38" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E38" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F38" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H38" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I38" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J38" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K38" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L38" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M38" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N38" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O38" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3691,12 +3683,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3718,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C39" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D39" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E39" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F39" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H39" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I39" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J39" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K39" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L39" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M39" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O39" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,7 +3768,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3798,50 +3792,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C40" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D40" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E40" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H40" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I40" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J40" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K40" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L40" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M40" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N40" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O40" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3851,12 +3845,12 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3873,55 +3867,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C41" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D41" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E41" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F41" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H41" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I41" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J41" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K41" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L41" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M41" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N41" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O41" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3929,18 +3927,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3955,79 +3953,85 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C42" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D42" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E42" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F42" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H42" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I42" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J42" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K42" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L42" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M42" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N42" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O42" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4039,85 +4043,79 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C43" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D43" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E43" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F43" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H43" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I43" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J43" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K43" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L43" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M43" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N43" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O43" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4136,50 +4134,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C44" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D44" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E44" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F44" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H44" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I44" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J44" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K44" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L44" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M44" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N44" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O44" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4187,18 +4185,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4211,72 +4209,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C45" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D45" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E45" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F45" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H45" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I45" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J45" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K45" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L45" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M45" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N45" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O45" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4300,74 +4298,70 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C46" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D46" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E46" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F46" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H46" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I46" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J46" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K46" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L46" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M46" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N46" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O46" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4379,55 +4373,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C47" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D47" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E47" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F47" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H47" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I47" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J47" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K47" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L47" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M47" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N47" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O47" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4438,15 +4436,13 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4461,57 +4457,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C48" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D48" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E48" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F48" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H48" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I48" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K48" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L48" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M48" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N48" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O48" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,78 +4518,78 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C49" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D49" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E49" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F49" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H49" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I49" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J49" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K49" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L49" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N49" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O49" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4604,20 +4600,16 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4627,55 +4619,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C50" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D50" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E50" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F50" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H50" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I50" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J50" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K50" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L50" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M50" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N50" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O50" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4683,19 +4679,25 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4707,57 +4709,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C51" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D51" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E51" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F51" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H51" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I51" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J51" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K51" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L51" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M51" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O51" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4765,25 +4767,21 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4802,50 +4800,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C52" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D52" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E52" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F52" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H52" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I52" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J52" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K52" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L52" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M52" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N52" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O52" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4858,13 +4856,11 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4879,57 +4875,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C53" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D53" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E53" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F53" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H53" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I53" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J53" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K53" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L53" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M53" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N53" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O53" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4937,12 +4933,14 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4961,57 +4959,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C54" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D54" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E54" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F54" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H54" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I54" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J54" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K54" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L54" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M54" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N54" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O54" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5019,14 +5017,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5045,57 +5041,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C55" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D55" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E55" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F55" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H55" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I55" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J55" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K55" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L55" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M55" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N55" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O55" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5108,11 +5104,13 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5127,76 +5125,78 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3920.27</v>
+        <v>3878.41</v>
       </c>
       <c r="C56" t="n">
-        <v>3967.68</v>
+        <v>3878.41</v>
       </c>
       <c r="D56" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E56" t="n">
-        <v>3888.37</v>
+        <v>3842.19</v>
       </c>
       <c r="F56" t="n">
-        <v>-23.5</v>
+        <v>-46.18</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0119</v>
       </c>
       <c r="H56" t="n">
-        <v>79.31</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>3765.77</v>
+        <v>3809.07</v>
       </c>
       <c r="J56" t="n">
-        <v>3850.26</v>
+        <v>3789.24</v>
       </c>
       <c r="K56" t="n">
-        <v>3873.4</v>
+        <v>3848.72</v>
       </c>
       <c r="L56" t="n">
-        <v>3896.53</v>
+        <v>3908.2</v>
       </c>
       <c r="M56" t="n">
-        <v>3950.35</v>
+        <v>3928.03</v>
       </c>
       <c r="N56" t="n">
-        <v>4004.16</v>
+        <v>3947.85</v>
       </c>
       <c r="O56" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
+        <v>4046.99</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5210,92 +5210,6 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3878.41</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3878.41</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3806.67</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3842.19</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-46.18</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0119</v>
-      </c>
-      <c r="H57" t="n">
-        <v>71.73999999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3809.07</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3789.24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3848.72</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3908.2</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3928.03</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3947.85</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4046.99</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5145,7 +5145,7 @@
         <v>3806.67</v>
       </c>
       <c r="E56" t="n">
-        <v>3842.19</v>
+        <v>3842.2</v>
       </c>
       <c r="F56" t="n">
         <v>-46.18</v>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>101.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3580.37</v>
+        <v>3597.29</v>
       </c>
       <c r="J2" t="n">
-        <v>3661.76</v>
+        <v>3682.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3736.28</v>
+        <v>3744.74</v>
       </c>
       <c r="L2" t="n">
-        <v>3810.8</v>
+        <v>3806.56</v>
       </c>
       <c r="M2" t="n">
-        <v>3888.75</v>
+        <v>3880.29</v>
       </c>
       <c r="N2" t="n">
-        <v>3966.71</v>
+        <v>3954.01</v>
       </c>
       <c r="O2" t="n">
-        <v>4037.79</v>
+        <v>4003.94</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>101.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3597.29</v>
+        <v>3648.52</v>
       </c>
       <c r="J2" t="n">
-        <v>3682.92</v>
+        <v>3746.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3744.74</v>
+        <v>3770.35</v>
       </c>
       <c r="L2" t="n">
-        <v>3806.56</v>
+        <v>3793.76</v>
       </c>
       <c r="M2" t="n">
-        <v>3880.29</v>
+        <v>3854.67</v>
       </c>
       <c r="N2" t="n">
-        <v>3954.01</v>
+        <v>3915.59</v>
       </c>
       <c r="O2" t="n">
-        <v>4003.94</v>
+        <v>3901.48</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5215,6 +5218,90 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3838.98</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3838.98</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3838.98</v>
+      </c>
+      <c r="E57" t="n">
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3734.93</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3770.28</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3806.33</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3842.37</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3878.06</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3913.76</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3950.15</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>101.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3648.52</v>
+        <v>3673.46</v>
       </c>
       <c r="J2" t="n">
-        <v>3746.95</v>
+        <v>3756.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3770.35</v>
+        <v>3776.59</v>
       </c>
       <c r="L2" t="n">
-        <v>3793.76</v>
+        <v>3796.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3854.67</v>
+        <v>3848.44</v>
       </c>
       <c r="N2" t="n">
-        <v>3915.59</v>
+        <v>3900</v>
       </c>
       <c r="O2" t="n">
-        <v>3901.48</v>
+        <v>3889.01</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,14 +695,16 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5228,22 +5227,22 @@
         <v>3838.98</v>
       </c>
       <c r="C57" t="n">
-        <v>3838.98</v>
+        <v>3864.12</v>
       </c>
       <c r="D57" t="n">
-        <v>3838.98</v>
+        <v>3795.37</v>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>3811.9</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>-30.29</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v/>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>3734.93</v>
@@ -5266,20 +5265,20 @@
       <c r="O57" t="n">
         <v>3950.15</v>
       </c>
-      <c r="P57" s="6" t="inlineStr">
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5298,7 +5297,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3811.67</v>
+        <v>3876.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3892.74</v>
+        <v>3899.96</v>
       </c>
       <c r="D2" t="n">
-        <v>3791.72</v>
+        <v>3801</v>
       </c>
       <c r="E2" t="n">
-        <v>3870.6</v>
+        <v>3820.09</v>
       </c>
       <c r="F2" t="n">
-        <v>58.08</v>
+        <v>-50.51</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0152</v>
+        <v>-0.013</v>
       </c>
       <c r="H2" t="n">
-        <v>101.01</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3673.46</v>
+        <v>3690.71</v>
       </c>
       <c r="J2" t="n">
-        <v>3756.3</v>
+        <v>3783.77</v>
       </c>
       <c r="K2" t="n">
-        <v>3776.59</v>
+        <v>3820.09</v>
       </c>
       <c r="L2" t="n">
-        <v>3796.87</v>
+        <v>3856.41</v>
       </c>
       <c r="M2" t="n">
-        <v>3848.44</v>
+        <v>3921.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3900</v>
+        <v>3985.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3889.01</v>
+        <v>3993.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,81 +685,83 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3876.1</v>
+        <v>3822.01</v>
       </c>
       <c r="C3" t="n">
-        <v>3899.96</v>
+        <v>3866.11</v>
       </c>
       <c r="D3" t="n">
-        <v>3801</v>
+        <v>3774.53</v>
       </c>
       <c r="E3" t="n">
-        <v>3820.09</v>
+        <v>3828.11</v>
       </c>
       <c r="F3" t="n">
-        <v>-50.51</v>
+        <v>8.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0021</v>
       </c>
       <c r="H3" t="n">
-        <v>98.95999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="I3" t="n">
-        <v>3690.71</v>
+        <v>3702.03</v>
       </c>
       <c r="J3" t="n">
-        <v>3783.77</v>
+        <v>3705.93</v>
       </c>
       <c r="K3" t="n">
-        <v>3820.09</v>
+        <v>3770.61</v>
       </c>
       <c r="L3" t="n">
-        <v>3856.41</v>
+        <v>3835.28</v>
       </c>
       <c r="M3" t="n">
-        <v>3921.1</v>
+        <v>3869.57</v>
       </c>
       <c r="N3" t="n">
-        <v>3985.8</v>
+        <v>3903.86</v>
       </c>
       <c r="O3" t="n">
-        <v>3993.75</v>
+        <v>3998.92</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,14 +769,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C4" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D4" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E4" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F4" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H4" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3702.03</v>
+        <v>3682.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3705.93</v>
+        <v>3740.42</v>
       </c>
       <c r="K4" t="n">
-        <v>3770.61</v>
+        <v>3782.32</v>
       </c>
       <c r="L4" t="n">
-        <v>3835.28</v>
+        <v>3824.21</v>
       </c>
       <c r="M4" t="n">
-        <v>3869.57</v>
+        <v>3873.89</v>
       </c>
       <c r="N4" t="n">
-        <v>3903.86</v>
+        <v>3923.58</v>
       </c>
       <c r="O4" t="n">
-        <v>3998.92</v>
+        <v>3957.68</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,11 +856,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -873,59 +875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C5" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D5" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E5" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F5" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H5" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I5" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K5" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L5" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M5" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N5" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O5" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,7 +934,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -962,68 +960,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C6" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D6" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F6" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H6" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I6" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J6" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K6" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L6" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M6" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N6" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>3987.41</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1037,84 +1041,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C7" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D7" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E7" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F7" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H7" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I7" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J7" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L7" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M7" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N7" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O7" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1123,59 +1127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C8" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D8" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E8" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F8" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H8" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I8" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L8" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N8" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O8" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,9 +1186,9 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1196,10 +1196,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1214,50 +1212,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C9" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D9" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E9" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F9" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H9" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I9" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J9" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K9" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L9" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M9" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N9" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,19 +1266,21 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1289,55 +1289,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C10" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D10" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E10" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F10" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H10" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J10" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K10" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L10" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M10" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N10" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O10" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,20 +1352,16 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1373,70 +1373,76 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C11" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E11" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H11" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J11" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L11" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M11" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N11" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O11" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>4087.48</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1448,83 +1454,73 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C12" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D12" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E12" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F12" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H12" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J12" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K12" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L12" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M12" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N12" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4150.06</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1541,55 +1537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C13" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D13" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E13" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F13" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H13" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I13" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J13" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K13" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L13" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M13" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O13" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,13 +1600,15 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1621,75 +1623,79 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C14" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D14" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E14" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F14" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H14" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J14" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K14" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L14" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M14" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N14" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1705,80 +1711,76 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C15" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D15" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E15" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H15" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I15" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J15" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K15" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L15" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O15" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1800,50 +1802,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C16" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D16" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E16" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H16" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I16" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J16" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K16" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L16" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N16" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O16" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,24 +1853,26 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
@@ -1877,57 +1881,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C17" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D17" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E17" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F17" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H17" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I17" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J17" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K17" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L17" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M17" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N17" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,23 +1942,19 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1970,50 +1970,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C18" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D18" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E18" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F18" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H18" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I18" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J18" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L18" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M18" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N18" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O18" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,78 +2024,80 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C19" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D19" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E19" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F19" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H19" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I19" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J19" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K19" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L19" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O19" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,9 +2108,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2116,70 +2118,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C20" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D20" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E20" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I20" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J20" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K20" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L20" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M20" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N20" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O20" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,15 +2192,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2213,74 +2213,80 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C21" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D21" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E21" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F21" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H21" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I21" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J21" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K21" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L21" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M21" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N21" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O21" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,50 +2308,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C22" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D22" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E22" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F22" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H22" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I22" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J22" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K22" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L22" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M22" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N22" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O22" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2357,18 +2363,16 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2383,79 +2387,77 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C23" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D23" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E23" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F23" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H23" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I23" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J23" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K23" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L23" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M23" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O23" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2467,59 +2469,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C24" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D24" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E24" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F24" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H24" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I24" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J24" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K24" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L24" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M24" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N24" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O24" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,9 +2528,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2540,8 +2538,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2556,63 +2556,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C25" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D25" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E25" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F25" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I25" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J25" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K25" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L25" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M25" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N25" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O25" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2620,10 +2624,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2633,78 +2635,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C26" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D26" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E26" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F26" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H26" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K26" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L26" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M26" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O26" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2719,72 +2721,76 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C27" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D27" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E27" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H27" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I27" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J27" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K27" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L27" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M27" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N27" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O27" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2796,81 +2802,75 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C28" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D28" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E28" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F28" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H28" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I28" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J28" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K28" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L28" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M28" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O28" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2894,67 +2894,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C29" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D29" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H29" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I29" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J29" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K29" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L29" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M29" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N29" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O29" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
       </c>
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2971,55 +2967,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C30" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D30" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E30" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F30" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H30" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I30" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J30" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K30" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L30" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M30" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N30" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O30" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3032,76 +3032,76 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C31" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D31" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E31" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F31" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H31" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I31" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J31" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K31" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L31" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M31" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N31" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O31" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,20 +3112,18 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3140,50 +3138,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C32" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D32" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E32" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F32" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H32" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I32" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J32" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K32" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L32" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M32" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N32" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O32" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3194,7 +3192,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3220,50 +3218,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C33" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D33" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E33" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F33" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I33" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J33" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K33" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L33" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M33" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N33" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O33" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,7 +3272,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3300,50 +3298,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C34" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D34" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E34" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F34" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H34" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I34" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J34" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K34" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L34" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M34" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N34" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O34" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3354,21 +3352,25 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3380,63 +3382,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C35" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D35" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E35" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F35" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H35" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I35" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J35" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K35" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L35" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M35" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N35" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O35" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3446,7 +3452,7 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V35" s="8" t="inlineStr">
@@ -3454,152 +3460,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C36" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D36" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E36" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F36" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H36" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I36" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J36" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K36" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L36" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M36" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N36" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O36" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C37" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D37" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E37" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F37" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H37" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J37" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K37" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L37" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M37" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N37" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O37" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,12 +3603,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3634,50 +3632,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C38" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D38" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E38" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F38" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I38" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J38" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K38" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L38" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M38" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N38" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O38" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3690,7 +3688,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3714,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C39" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D39" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E39" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F39" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H39" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I39" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J39" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K39" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L39" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M39" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N39" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O39" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,12 +3765,12 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3789,55 +3787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C40" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D40" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E40" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F40" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H40" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I40" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J40" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K40" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L40" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M40" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N40" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O40" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3845,18 +3847,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3871,79 +3873,85 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C41" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D41" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E41" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F41" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H41" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I41" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J41" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K41" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L41" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M41" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N41" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O41" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3955,85 +3963,79 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C42" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D42" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E42" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F42" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H42" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I42" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J42" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K42" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L42" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M42" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N42" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O42" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4052,50 +4054,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C43" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D43" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E43" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F43" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H43" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I43" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J43" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K43" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L43" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M43" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N43" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O43" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4103,18 +4105,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4127,72 +4129,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C44" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D44" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E44" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F44" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H44" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I44" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J44" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K44" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L44" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M44" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N44" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O44" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4216,74 +4218,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C45" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D45" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E45" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F45" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H45" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I45" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J45" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L45" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M45" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N45" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O45" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4295,55 +4293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C46" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D46" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E46" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F46" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H46" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I46" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J46" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K46" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L46" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M46" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N46" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O46" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4354,15 +4356,13 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4377,57 +4377,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C47" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D47" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E47" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F47" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H47" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I47" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J47" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K47" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L47" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M47" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N47" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O47" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4438,78 +4438,78 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C48" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D48" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E48" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F48" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H48" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I48" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J48" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K48" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L48" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N48" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O48" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4520,20 +4520,16 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4543,55 +4539,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C49" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D49" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E49" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F49" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H49" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I49" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J49" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K49" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L49" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M49" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N49" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O49" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,19 +4599,25 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4623,57 +4629,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C50" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D50" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E50" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F50" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H50" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I50" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J50" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K50" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L50" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M50" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N50" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O50" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4681,25 +4687,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4718,50 +4720,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C51" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D51" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E51" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F51" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H51" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I51" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J51" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K51" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L51" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M51" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N51" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O51" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4774,13 +4776,11 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4795,57 +4795,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C52" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D52" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E52" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F52" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H52" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I52" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J52" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K52" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L52" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M52" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N52" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O52" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4853,12 +4853,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4877,57 +4879,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C53" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D53" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E53" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F53" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H53" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I53" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J53" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K53" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L53" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M53" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N53" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O53" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4935,14 +4937,12 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4961,57 +4961,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C54" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D54" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E54" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F54" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H54" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I54" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J54" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K54" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L54" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N54" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O54" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5024,11 +5024,13 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5043,76 +5045,78 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3920.27</v>
+        <v>3878.41</v>
       </c>
       <c r="C55" t="n">
-        <v>3967.68</v>
+        <v>3878.41</v>
       </c>
       <c r="D55" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E55" t="n">
-        <v>3888.37</v>
+        <v>3842.2</v>
       </c>
       <c r="F55" t="n">
-        <v>-23.5</v>
+        <v>-46.18</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0119</v>
       </c>
       <c r="H55" t="n">
-        <v>79.31</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>3765.77</v>
+        <v>3809.07</v>
       </c>
       <c r="J55" t="n">
-        <v>3850.26</v>
+        <v>3789.24</v>
       </c>
       <c r="K55" t="n">
-        <v>3873.4</v>
+        <v>3848.72</v>
       </c>
       <c r="L55" t="n">
-        <v>3896.53</v>
+        <v>3908.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3950.35</v>
+        <v>3928.03</v>
       </c>
       <c r="N55" t="n">
-        <v>4004.16</v>
+        <v>3947.85</v>
       </c>
       <c r="O55" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>4046.99</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5127,72 +5131,72 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3878.41</v>
+        <v>3838.98</v>
       </c>
       <c r="C56" t="n">
-        <v>3878.41</v>
+        <v>3864.12</v>
       </c>
       <c r="D56" t="n">
-        <v>3806.67</v>
+        <v>3754.14</v>
       </c>
       <c r="E56" t="n">
-        <v>3842.2</v>
+        <v>3813.79</v>
       </c>
       <c r="F56" t="n">
-        <v>-46.18</v>
+        <v>-28.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0074</v>
       </c>
       <c r="H56" t="n">
-        <v>71.73999999999999</v>
+        <v>109.98</v>
       </c>
       <c r="I56" t="n">
-        <v>3809.07</v>
+        <v>3734.93</v>
       </c>
       <c r="J56" t="n">
-        <v>3789.24</v>
+        <v>3770.28</v>
       </c>
       <c r="K56" t="n">
-        <v>3848.72</v>
+        <v>3806.33</v>
       </c>
       <c r="L56" t="n">
-        <v>3908.2</v>
+        <v>3842.37</v>
       </c>
       <c r="M56" t="n">
-        <v>3928.03</v>
+        <v>3878.06</v>
       </c>
       <c r="N56" t="n">
-        <v>3947.85</v>
+        <v>3913.76</v>
       </c>
       <c r="O56" t="n">
-        <v>4046.99</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>3950.15</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5212,90 +5216,6 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3838.98</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3864.12</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3795.37</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3811.9</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-30.29</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.007900000000000001</v>
-      </c>
-      <c r="H57" t="n">
-        <v>68.73999999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3734.93</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3770.28</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3806.33</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3842.37</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3878.06</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3913.76</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3950.15</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5221,6 +5221,88 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3806.98</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3828.22</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3797.24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-16.55</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="H57" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3644.15</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3706.14</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3758.8</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3811.46</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3868.78</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3926.11</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3974.1</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>98.95999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3690.71</v>
+        <v>3695.38</v>
       </c>
       <c r="J2" t="n">
-        <v>3783.77</v>
+        <v>3785.52</v>
       </c>
       <c r="K2" t="n">
-        <v>3820.09</v>
+        <v>3821.26</v>
       </c>
       <c r="L2" t="n">
-        <v>3856.41</v>
+        <v>3857</v>
       </c>
       <c r="M2" t="n">
-        <v>3921.1</v>
+        <v>3919.94</v>
       </c>
       <c r="N2" t="n">
-        <v>3985.8</v>
+        <v>3982.88</v>
       </c>
       <c r="O2" t="n">
-        <v>3993.75</v>
+        <v>3991.42</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5234,19 +5234,19 @@
         <v>3828.22</v>
       </c>
       <c r="D57" t="n">
-        <v>3791</v>
+        <v>3741.53</v>
       </c>
       <c r="E57" t="n">
-        <v>3797.24</v>
+        <v>3800.86</v>
       </c>
       <c r="F57" t="n">
-        <v>-16.55</v>
+        <v>-12.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0034</v>
       </c>
       <c r="H57" t="n">
-        <v>37.22</v>
+        <v>86.69</v>
       </c>
       <c r="I57" t="n">
         <v>3644.15</v>
@@ -5275,8 +5275,10 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
@@ -5299,7 +5301,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>98.95999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3695.38</v>
+        <v>3700.13</v>
       </c>
       <c r="J2" t="n">
-        <v>3785.52</v>
+        <v>3787.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3821.26</v>
+        <v>3822.45</v>
       </c>
       <c r="L2" t="n">
-        <v>3857</v>
+        <v>3857.59</v>
       </c>
       <c r="M2" t="n">
-        <v>3919.94</v>
+        <v>3918.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3982.88</v>
+        <v>3979.91</v>
       </c>
       <c r="O2" t="n">
-        <v>3991.42</v>
+        <v>3989.04</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5237,13 +5237,13 @@
         <v>3741.53</v>
       </c>
       <c r="E57" t="n">
-        <v>3800.86</v>
+        <v>3767.23</v>
       </c>
       <c r="F57" t="n">
-        <v>-12.93</v>
+        <v>-46.56</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0122</v>
       </c>
       <c r="H57" t="n">
         <v>86.69</v>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,35 +659,39 @@
         <v>98.95999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3700.13</v>
+        <v>3840.34</v>
       </c>
       <c r="J2" t="n">
-        <v>3787.3</v>
+        <v>3839.88</v>
       </c>
       <c r="K2" t="n">
-        <v>3822.45</v>
+        <v>3857.5</v>
       </c>
       <c r="L2" t="n">
-        <v>3857.59</v>
+        <v>3875.12</v>
       </c>
       <c r="M2" t="n">
-        <v>3918.75</v>
+        <v>3883.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3979.91</v>
+        <v>3892.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3989.04</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>3918.94</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -695,18 +699,22 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -788,12 +796,12 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -872,10 +880,14 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -952,10 +964,14 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1038,14 +1054,10 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1124,10 +1136,14 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1204,10 +1220,14 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1286,12 +1306,12 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1388,12 @@
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1474,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1532,7 +1552,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1616,7 +1636,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1704,7 +1724,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1788,7 +1808,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1874,7 +1894,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1956,7 +1976,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2044,7 +2064,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2124,7 +2144,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2206,7 +2226,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2294,7 +2314,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2380,7 +2400,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2464,7 +2484,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2546,7 +2566,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2630,7 +2650,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2714,7 +2734,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2802,7 +2822,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2884,7 +2904,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2962,7 +2982,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3048,7 +3068,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3128,7 +3148,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3208,7 +3228,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3288,7 +3308,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3372,7 +3392,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3460,7 +3480,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3542,7 +3562,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3622,7 +3642,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3702,7 +3722,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3782,7 +3802,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3866,7 +3886,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3956,7 +3976,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4040,7 +4060,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4124,7 +4144,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4208,7 +4228,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4288,7 +4308,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4370,7 +4390,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4456,7 +4476,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4534,7 +4554,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4622,7 +4642,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4706,7 +4726,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4788,7 +4808,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4872,7 +4892,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4954,7 +4974,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5038,7 +5058,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5124,7 +5144,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5210,7 +5230,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5234,19 +5254,19 @@
         <v>3828.22</v>
       </c>
       <c r="D57" t="n">
-        <v>3741.53</v>
+        <v>3674.82</v>
       </c>
       <c r="E57" t="n">
-        <v>3767.23</v>
+        <v>3707.48</v>
       </c>
       <c r="F57" t="n">
-        <v>-46.56</v>
+        <v>-106.31</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0122</v>
+        <v>-0.0279</v>
       </c>
       <c r="H57" t="n">
-        <v>86.69</v>
+        <v>153.4</v>
       </c>
       <c r="I57" t="n">
         <v>3644.15</v>
@@ -5272,12 +5292,14 @@
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -5294,7 +5316,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,142 +634,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3876.1</v>
+        <v>3822.01</v>
       </c>
       <c r="C2" t="n">
-        <v>3899.96</v>
+        <v>3866.11</v>
       </c>
       <c r="D2" t="n">
-        <v>3801</v>
+        <v>3774.53</v>
       </c>
       <c r="E2" t="n">
-        <v>3820.09</v>
+        <v>3828.11</v>
       </c>
       <c r="F2" t="n">
-        <v>-50.51</v>
+        <v>8.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0021</v>
       </c>
       <c r="H2" t="n">
-        <v>98.95999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="I2" t="n">
-        <v>3840.34</v>
+        <v>3702.03</v>
       </c>
       <c r="J2" t="n">
-        <v>3839.88</v>
+        <v>3705.93</v>
       </c>
       <c r="K2" t="n">
-        <v>3857.5</v>
+        <v>3770.61</v>
       </c>
       <c r="L2" t="n">
-        <v>3875.12</v>
+        <v>3835.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3883.7</v>
+        <v>3869.57</v>
       </c>
       <c r="N2" t="n">
-        <v>3892.28</v>
+        <v>3903.86</v>
       </c>
       <c r="O2" t="n">
-        <v>3918.94</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3998.92</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C3" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D3" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E3" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F3" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H3" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3702.03</v>
+        <v>3682.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3705.93</v>
+        <v>3740.42</v>
       </c>
       <c r="K3" t="n">
-        <v>3770.61</v>
+        <v>3782.32</v>
       </c>
       <c r="L3" t="n">
-        <v>3835.28</v>
+        <v>3824.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3869.57</v>
+        <v>3873.89</v>
       </c>
       <c r="N3" t="n">
-        <v>3903.86</v>
+        <v>3923.58</v>
       </c>
       <c r="O3" t="n">
-        <v>3998.92</v>
+        <v>3957.68</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,13 +770,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -796,62 +788,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C4" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D4" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E4" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F4" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H4" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I4" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L4" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M4" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N4" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O4" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -880,80 +868,82 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D5" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F5" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H5" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I5" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J5" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K5" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L5" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M5" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N5" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>3987.41</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -964,7 +954,7 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -976,85 +966,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C6" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D6" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E6" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F6" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H6" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I6" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J6" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L6" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M6" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N6" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1062,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C7" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D7" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E7" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F7" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H7" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I7" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J7" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L7" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N7" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O7" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1118,7 +1104,7 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1126,72 +1112,66 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C8" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D8" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E8" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F8" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H8" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I8" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L8" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M8" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N8" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1204,78 +1184,80 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C9" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D9" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E9" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F9" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I9" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J9" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K9" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L9" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M9" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N9" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O9" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1288,25 +1270,21 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1318,63 +1296,69 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C10" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E10" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H10" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J10" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K10" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L10" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M10" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N10" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O10" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4087.48</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1386,83 +1370,73 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C11" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D11" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E11" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H11" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J11" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K11" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L11" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M11" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N11" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4150.06</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1474,60 +1448,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C12" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D12" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E12" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F12" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H12" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I12" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J12" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L12" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O12" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1540,11 +1518,13 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1552,82 +1532,86 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C13" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D13" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E13" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F13" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H13" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J13" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K13" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L13" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N13" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1636,87 +1620,83 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C14" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D14" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E14" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I14" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J14" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K14" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L14" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O14" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1724,7 +1704,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1738,50 +1718,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C15" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D15" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E15" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H15" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I15" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J15" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K15" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L15" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N15" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O15" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1789,83 +1769,85 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C16" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D16" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E16" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F16" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H16" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I16" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J16" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K16" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L16" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M16" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N16" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1878,23 +1860,19 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1908,50 +1886,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C17" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D17" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E17" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F17" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H17" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I17" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K17" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L17" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M17" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N17" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O17" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1964,76 +1942,78 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C18" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D18" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E18" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F18" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H18" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I18" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J18" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K18" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L18" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M18" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O18" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2046,7 +2026,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2054,70 +2034,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C19" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D19" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E19" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I19" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J19" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K19" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L19" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M19" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N19" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O19" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2133,10 +2113,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2144,81 +2122,87 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C20" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D20" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E20" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F20" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H20" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I20" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J20" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K20" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L20" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M20" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N20" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O20" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2226,7 +2210,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2240,50 +2224,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C21" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D21" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E21" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H21" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I21" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J21" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K21" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L21" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M21" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N21" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O21" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2295,18 +2279,16 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2314,150 +2296,144 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C22" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D22" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E22" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F22" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H22" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I22" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J22" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K22" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L22" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M22" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O22" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C23" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D23" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E23" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F23" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H23" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I23" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J23" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K23" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L23" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M23" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N23" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O23" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2470,7 +2446,7 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2478,13 +2454,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2494,63 +2472,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C24" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D24" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E24" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F24" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I24" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J24" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K24" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L24" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M24" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N24" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O24" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2558,91 +2540,89 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C25" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D25" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E25" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F25" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H25" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K25" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L25" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M25" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O25" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2650,70 +2630,74 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C26" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D26" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E26" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F26" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H26" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I26" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J26" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K26" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L26" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M26" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N26" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O26" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2722,7 +2706,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2736,78 +2720,72 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C27" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D27" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E27" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F27" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H27" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I27" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J27" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K27" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L27" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M27" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O27" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2822,7 +2800,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2832,67 +2810,63 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C28" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D28" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E28" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H28" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I28" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J28" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K28" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L28" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M28" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N28" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O28" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
       </c>
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2904,60 +2878,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C29" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D29" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E29" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F29" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H29" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I29" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J29" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K29" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L29" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M29" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N29" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O29" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2968,78 +2946,78 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C30" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D30" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E30" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F30" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H30" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I30" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J30" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K30" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L30" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M30" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O30" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3057,18 +3035,16 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3078,50 +3054,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C31" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D31" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E31" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F31" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H31" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I31" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J31" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K31" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L31" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M31" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N31" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O31" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3148,7 +3124,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3158,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C32" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D32" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E32" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F32" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I32" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J32" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K32" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L32" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M32" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N32" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O32" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3228,7 +3204,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3238,50 +3214,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C33" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D33" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E33" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F33" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H33" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I33" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J33" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K33" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L33" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M33" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N33" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O33" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3299,16 +3275,20 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3318,63 +3298,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C34" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D34" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E34" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F34" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H34" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I34" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J34" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K34" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L34" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M34" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N34" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O34" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3384,7 +3368,7 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
@@ -3394,150 +3378,140 @@
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C35" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D35" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E35" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F35" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H35" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I35" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J35" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K35" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L35" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M35" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N35" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O35" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C36" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D36" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E36" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F36" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H36" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I36" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J36" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K36" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L36" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M36" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N36" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O36" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,12 +3519,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3562,7 +3538,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3572,50 +3548,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C37" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D37" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E37" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F37" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I37" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J37" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K37" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L37" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M37" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O37" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3642,7 +3618,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3652,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C38" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D38" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E38" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F38" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H38" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I38" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J38" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K38" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L38" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M38" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N38" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O38" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,12 +3681,12 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3722,60 +3698,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C39" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D39" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E39" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F39" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H39" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I39" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J39" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K39" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L39" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M39" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N39" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O39" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3783,18 +3763,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3802,181 +3782,181 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C40" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D40" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E40" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F40" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H40" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I40" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J40" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K40" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L40" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M40" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N40" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O40" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C41" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D41" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E41" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F41" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H41" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I41" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J41" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K41" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L41" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M41" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N41" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O41" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3990,50 +3970,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C42" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D42" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E42" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F42" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H42" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I42" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J42" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K42" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L42" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M42" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N42" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O42" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4041,18 +4021,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4060,74 +4040,74 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C43" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D43" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E43" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F43" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H43" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I43" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J43" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K43" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L43" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M43" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N43" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O43" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -4144,7 +4124,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4154,134 +4134,134 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C44" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D44" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E44" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F44" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H44" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I44" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J44" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K44" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L44" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M44" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N44" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O44" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C45" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D45" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E45" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F45" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H45" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I45" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J45" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K45" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L45" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N45" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O45" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4297,10 +4277,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4308,64 +4286,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C46" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D46" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E46" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F46" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H46" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I46" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K46" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L46" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M46" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N46" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O46" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4378,76 +4356,76 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C47" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D47" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E47" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F47" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H47" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I47" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J47" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K47" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L47" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M47" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N47" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O47" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4460,76 +4438,76 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C48" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D48" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E48" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H48" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I48" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J48" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K48" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L48" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M48" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N48" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O48" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4537,81 +4515,87 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C49" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D49" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E49" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F49" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H49" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I49" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J49" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K49" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L49" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M49" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N49" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O49" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4619,30 +4603,26 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4656,50 +4636,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C50" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D50" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E50" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F50" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H50" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I50" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J50" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K50" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L50" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M50" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N50" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O50" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4710,15 +4690,13 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4726,64 +4704,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C51" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D51" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E51" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F51" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H51" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I51" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J51" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K51" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L51" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M51" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N51" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O51" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4791,12 +4769,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4808,64 +4788,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C52" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D52" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E52" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F52" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H52" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I52" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J52" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K52" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L52" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M52" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N52" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O52" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4873,14 +4853,12 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4892,64 +4870,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C53" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D53" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E53" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F53" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H53" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I53" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J53" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K53" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L53" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N53" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O53" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4960,13 +4938,15 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4974,83 +4954,85 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3920.27</v>
+        <v>3878.41</v>
       </c>
       <c r="C54" t="n">
-        <v>3967.68</v>
+        <v>3878.41</v>
       </c>
       <c r="D54" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E54" t="n">
-        <v>3888.37</v>
+        <v>3842.2</v>
       </c>
       <c r="F54" t="n">
-        <v>-23.5</v>
+        <v>-46.18</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0119</v>
       </c>
       <c r="H54" t="n">
-        <v>79.31</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>3765.77</v>
+        <v>3809.07</v>
       </c>
       <c r="J54" t="n">
-        <v>3850.26</v>
+        <v>3789.24</v>
       </c>
       <c r="K54" t="n">
-        <v>3873.4</v>
+        <v>3848.72</v>
       </c>
       <c r="L54" t="n">
-        <v>3896.53</v>
+        <v>3908.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3950.35</v>
+        <v>3928.03</v>
       </c>
       <c r="N54" t="n">
-        <v>4004.16</v>
+        <v>3947.85</v>
       </c>
       <c r="O54" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>4046.99</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5058,73 +5040,73 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3878.41</v>
+        <v>3838.98</v>
       </c>
       <c r="C55" t="n">
-        <v>3878.41</v>
+        <v>3864.12</v>
       </c>
       <c r="D55" t="n">
-        <v>3806.67</v>
+        <v>3754.14</v>
       </c>
       <c r="E55" t="n">
-        <v>3842.2</v>
+        <v>3813.79</v>
       </c>
       <c r="F55" t="n">
-        <v>-46.18</v>
+        <v>-28.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0074</v>
       </c>
       <c r="H55" t="n">
-        <v>71.73999999999999</v>
+        <v>109.98</v>
       </c>
       <c r="I55" t="n">
-        <v>3809.07</v>
+        <v>3734.93</v>
       </c>
       <c r="J55" t="n">
-        <v>3789.24</v>
+        <v>3770.28</v>
       </c>
       <c r="K55" t="n">
-        <v>3848.72</v>
+        <v>3806.33</v>
       </c>
       <c r="L55" t="n">
-        <v>3908.2</v>
+        <v>3842.37</v>
       </c>
       <c r="M55" t="n">
-        <v>3928.03</v>
+        <v>3878.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3947.85</v>
+        <v>3913.76</v>
       </c>
       <c r="O55" t="n">
-        <v>4046.99</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>3950.15</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
@@ -5144,7 +5126,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5158,64 +5140,64 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3838.98</v>
+        <v>3806.98</v>
       </c>
       <c r="C56" t="n">
-        <v>3864.12</v>
+        <v>3828.22</v>
       </c>
       <c r="D56" t="n">
-        <v>3754.14</v>
+        <v>3674.82</v>
       </c>
       <c r="E56" t="n">
-        <v>3813.79</v>
+        <v>3716.28</v>
       </c>
       <c r="F56" t="n">
-        <v>-28.4</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0256</v>
       </c>
       <c r="H56" t="n">
-        <v>109.98</v>
+        <v>153.4</v>
       </c>
       <c r="I56" t="n">
-        <v>3734.93</v>
+        <v>3644.15</v>
       </c>
       <c r="J56" t="n">
-        <v>3770.28</v>
+        <v>3706.14</v>
       </c>
       <c r="K56" t="n">
-        <v>3806.33</v>
+        <v>3758.8</v>
       </c>
       <c r="L56" t="n">
-        <v>3842.37</v>
+        <v>3811.46</v>
       </c>
       <c r="M56" t="n">
-        <v>3878.06</v>
+        <v>3868.78</v>
       </c>
       <c r="N56" t="n">
-        <v>3913.76</v>
+        <v>3926.11</v>
       </c>
       <c r="O56" t="n">
-        <v>3950.15</v>
+        <v>3974.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5230,98 +5212,12 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3806.98</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3828.22</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3674.82</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3707.48</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-106.31</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0279</v>
-      </c>
-      <c r="H57" t="n">
-        <v>153.4</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3644.15</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3706.14</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3758.8</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3811.46</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3868.78</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3926.11</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3974.1</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5223,6 +5226,90 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3694.12</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3743.8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3692.29</v>
+      </c>
+      <c r="E57" t="n">
+        <v/>
+      </c>
+      <c r="F57" t="n">
+        <v/>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3521.42</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3545.27</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3639.58</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3733.9</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3792.98</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3852.07</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3981.62</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5242,13 +5239,13 @@
         <v>3692.29</v>
       </c>
       <c r="E57" t="n">
-        <v/>
+        <v>3730.92</v>
       </c>
       <c r="F57" t="n">
-        <v/>
+        <v>14.64</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v/>
+        <v>0.0039</v>
       </c>
       <c r="H57" t="n">
         <v>51.51</v>
@@ -5274,10 +5271,8 @@
       <c r="O57" t="n">
         <v>3981.62</v>
       </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P57" s="6" t="n">
+        <v/>
       </c>
       <c r="Q57" s="6" t="n">
         <v/>
@@ -5285,9 +5280,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>3692.29</v>
       </c>
       <c r="E57" t="n">
-        <v>3730.92</v>
+        <v>3735.37</v>
       </c>
       <c r="F57" t="n">
-        <v>14.64</v>
+        <v>19.09</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0051</v>
       </c>
       <c r="H57" t="n">
         <v>51.51</v>
@@ -5280,9 +5280,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -5239,13 +5239,13 @@
         <v>3692.29</v>
       </c>
       <c r="E57" t="n">
-        <v>3735.37</v>
+        <v>3713.03</v>
       </c>
       <c r="F57" t="n">
-        <v>19.09</v>
+        <v>-3.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0009</v>
       </c>
       <c r="H57" t="n">
         <v>51.51</v>
@@ -5280,9 +5280,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,45 +659,55 @@
         <v>91.58</v>
       </c>
       <c r="I2" t="n">
-        <v>3702.03</v>
+        <v>3780.64</v>
       </c>
       <c r="J2" t="n">
-        <v>3705.93</v>
+        <v>3785.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3770.61</v>
+        <v>3804.46</v>
       </c>
       <c r="L2" t="n">
-        <v>3835.28</v>
+        <v>3823.81</v>
       </c>
       <c r="M2" t="n">
-        <v>3869.57</v>
+        <v>3835.72</v>
       </c>
       <c r="N2" t="n">
-        <v>3903.86</v>
+        <v>3847.63</v>
       </c>
       <c r="O2" t="n">
-        <v>3998.92</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>3874.44</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -709,7 +719,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -770,7 +780,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -850,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -936,7 +946,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1020,7 +1030,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1102,7 +1112,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1182,7 +1192,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1268,7 +1278,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1356,7 +1366,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1434,7 +1444,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1516,7 +1526,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1604,7 +1614,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1690,7 +1700,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1772,7 +1782,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1858,7 +1868,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1940,7 +1950,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2024,7 +2034,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2108,7 +2118,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2194,7 +2204,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2282,7 +2292,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2364,7 +2374,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2444,7 +2454,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2530,7 +2540,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2616,7 +2626,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2704,7 +2714,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2786,7 +2796,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2864,7 +2874,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2946,7 +2956,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3028,7 +3038,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3108,7 +3118,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3188,7 +3198,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3268,7 +3278,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3356,7 +3366,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3444,7 +3454,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3524,7 +3534,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3604,7 +3614,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3684,7 +3694,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3766,7 +3776,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3854,7 +3864,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3940,7 +3950,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4026,7 +4036,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4110,7 +4120,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4188,7 +4198,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4272,7 +4282,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4354,7 +4364,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4436,7 +4446,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4520,7 +4530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4606,7 +4616,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4690,7 +4700,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4774,7 +4784,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4856,7 +4866,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4938,7 +4948,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5026,7 +5036,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5112,7 +5122,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5198,7 +5208,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5236,19 +5246,19 @@
         <v>3743.8</v>
       </c>
       <c r="D57" t="n">
-        <v>3692.29</v>
+        <v>3649.86</v>
       </c>
       <c r="E57" t="n">
-        <v>3713.03</v>
+        <v>3658.03</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.26</v>
+        <v>-58.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0157</v>
       </c>
       <c r="H57" t="n">
-        <v>51.51</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>3521.42</v>
@@ -5277,12 +5287,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5301,7 +5313,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,80 +634,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3822.01</v>
+        <v>3828.17</v>
       </c>
       <c r="C2" t="n">
-        <v>3866.11</v>
+        <v>3887.57</v>
       </c>
       <c r="D2" t="n">
-        <v>3774.53</v>
+        <v>3809.53</v>
       </c>
       <c r="E2" t="n">
-        <v>3828.11</v>
+        <v>3882.78</v>
       </c>
       <c r="F2" t="n">
-        <v>8.02</v>
+        <v>54.67</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0143</v>
       </c>
       <c r="H2" t="n">
-        <v>91.58</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3780.64</v>
+        <v>3682.95</v>
       </c>
       <c r="J2" t="n">
-        <v>3785.1</v>
+        <v>3740.42</v>
       </c>
       <c r="K2" t="n">
-        <v>3804.46</v>
+        <v>3782.32</v>
       </c>
       <c r="L2" t="n">
-        <v>3823.81</v>
+        <v>3824.21</v>
       </c>
       <c r="M2" t="n">
-        <v>3835.72</v>
+        <v>3873.89</v>
       </c>
       <c r="N2" t="n">
-        <v>3847.63</v>
+        <v>3923.58</v>
       </c>
       <c r="O2" t="n">
-        <v>3874.44</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3957.68</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -717,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C3" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D3" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E3" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F3" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H3" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I3" t="n">
-        <v>3682.95</v>
+        <v>3731.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3740.42</v>
+        <v>3821.85</v>
       </c>
       <c r="K3" t="n">
-        <v>3782.32</v>
+        <v>3843.76</v>
       </c>
       <c r="L3" t="n">
-        <v>3824.21</v>
+        <v>3865.66</v>
       </c>
       <c r="M3" t="n">
-        <v>3873.89</v>
+        <v>3921.79</v>
       </c>
       <c r="N3" t="n">
-        <v>3923.58</v>
+        <v>3977.92</v>
       </c>
       <c r="O3" t="n">
-        <v>3957.68</v>
+        <v>3965.61</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -806,68 +794,74 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D4" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F4" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H4" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I4" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J4" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K4" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L4" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M4" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N4" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O4" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>3987.41</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -881,84 +875,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C5" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D5" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E5" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F5" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H5" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I5" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J5" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L5" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M5" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -967,59 +961,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D6" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E6" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F6" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H6" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I6" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J6" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L6" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N6" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O6" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1032,7 +1022,7 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1040,10 +1030,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1058,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C7" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D7" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E7" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F7" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H7" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I7" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J7" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K7" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L7" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M7" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N7" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,17 +1102,19 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1133,55 +1123,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C8" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D8" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E8" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F8" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J8" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K8" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L8" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M8" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N8" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O8" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,18 +1188,14 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1217,70 +1207,76 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C9" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E9" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H9" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J9" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L9" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M9" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N9" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O9" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4087.48</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1292,83 +1288,73 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C10" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D10" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E10" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H10" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J10" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K10" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L10" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M10" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N10" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O10" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4150.06</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1385,55 +1371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C11" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D11" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E11" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F11" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H11" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I11" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J11" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K11" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L11" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M11" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O11" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,11 +1436,13 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1465,75 +1457,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C12" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D12" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F12" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H12" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J12" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K12" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L12" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N12" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1549,80 +1545,76 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C13" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D13" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E13" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I13" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J13" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K13" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L13" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1644,50 +1636,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C14" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D14" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E14" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H14" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I14" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J14" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K14" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L14" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N14" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O14" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1695,24 +1687,26 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1721,57 +1715,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C15" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D15" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E15" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F15" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H15" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I15" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J15" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K15" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L15" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M15" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N15" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,21 +1778,17 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
@@ -1814,50 +1804,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C16" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D16" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E16" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F16" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H16" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I16" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J16" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L16" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M16" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N16" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O16" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1870,76 +1860,78 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C17" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D17" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E17" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F17" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H17" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I17" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J17" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K17" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L17" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O17" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1952,7 +1944,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1960,70 +1952,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C18" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D18" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E18" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I18" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J18" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K18" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L18" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M18" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N18" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O18" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2039,10 +2031,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2057,74 +2047,80 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C19" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D19" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E19" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F19" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H19" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I19" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J19" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K19" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L19" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M19" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N19" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O19" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2146,50 +2142,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C20" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D20" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E20" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H20" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I20" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J20" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K20" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L20" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M20" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N20" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O20" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,18 +2197,16 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2227,79 +2221,77 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C21" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D21" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E21" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F21" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H21" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I21" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J21" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K21" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L21" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M21" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N21" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O21" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2311,59 +2303,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C22" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D22" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E22" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F22" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H22" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I22" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J22" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K22" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L22" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M22" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N22" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O22" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2376,7 +2364,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2384,8 +2372,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2400,63 +2390,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C23" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D23" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E23" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F23" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I23" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J23" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K23" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L23" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M23" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N23" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O23" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2464,10 +2458,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2477,78 +2469,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C24" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D24" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E24" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F24" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H24" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K24" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L24" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O24" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2563,63 +2555,67 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C25" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D25" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E25" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F25" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H25" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I25" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J25" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K25" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L25" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M25" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N25" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O25" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2628,7 +2624,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2640,78 +2636,72 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C26" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D26" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E26" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F26" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H26" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I26" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J26" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K26" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L26" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O26" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2738,67 +2728,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C27" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D27" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E27" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H27" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I27" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J27" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K27" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L27" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M27" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N27" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O27" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
       </c>
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2815,55 +2801,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C28" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D28" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E28" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F28" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H28" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I28" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J28" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K28" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L28" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M28" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N28" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O28" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2874,78 +2864,78 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C29" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D29" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E29" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F29" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H29" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I29" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J29" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K29" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L29" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O29" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2963,13 +2953,11 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2984,50 +2972,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C30" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D30" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E30" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F30" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I30" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J30" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K30" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L30" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M30" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N30" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O30" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3064,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C31" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D31" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E31" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F31" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I31" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J31" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K31" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L31" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M31" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N31" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O31" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3144,50 +3132,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C32" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D32" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E32" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F32" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H32" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I32" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J32" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K32" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L32" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M32" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N32" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O32" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,14 +3193,18 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3224,63 +3216,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C33" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D33" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E33" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F33" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H33" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I33" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J33" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K33" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L33" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M33" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N33" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O33" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3290,7 +3286,7 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
@@ -3298,152 +3294,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C34" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D34" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E34" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F34" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H34" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I34" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J34" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K34" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L34" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M34" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N34" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O34" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C35" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D35" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E35" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F35" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H35" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I35" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J35" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K35" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L35" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M35" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N35" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O35" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,12 +3437,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3478,50 +3466,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C36" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D36" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E36" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F36" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H36" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I36" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J36" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K36" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L36" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M36" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N36" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O36" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3558,50 +3546,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C37" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D37" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E37" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F37" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H37" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I37" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J37" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K37" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L37" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M37" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N37" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O37" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,12 +3599,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3633,55 +3621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C38" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D38" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E38" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F38" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H38" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I38" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J38" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K38" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L38" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M38" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N38" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O38" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3689,18 +3681,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3715,79 +3707,85 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C39" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D39" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E39" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F39" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H39" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I39" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J39" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K39" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L39" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M39" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N39" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O39" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3799,85 +3797,79 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C40" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D40" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E40" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F40" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H40" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I40" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J40" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K40" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L40" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M40" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N40" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O40" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3896,50 +3888,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C41" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D41" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E41" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F41" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H41" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I41" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J41" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K41" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L41" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M41" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N41" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O41" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3947,18 +3939,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3971,69 +3963,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C42" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D42" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E42" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F42" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H42" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I42" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J42" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K42" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L42" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M42" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N42" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O42" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4060,74 +4052,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C43" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D43" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E43" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F43" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H43" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I43" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J43" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K43" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L43" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M43" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N43" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O43" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4139,55 +4127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C44" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D44" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E44" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F44" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H44" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I44" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J44" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K44" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L44" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M44" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N44" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O44" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4203,10 +4195,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4221,57 +4211,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C45" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D45" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E45" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F45" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H45" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I45" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J45" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K45" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L45" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M45" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N45" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O45" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,76 +4274,76 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C46" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D46" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E46" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F46" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H46" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I46" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J46" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K46" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L46" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M46" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N46" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O46" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,18 +4356,14 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4387,55 +4373,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C47" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D47" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E47" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F47" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H47" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I47" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J47" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K47" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L47" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M47" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N47" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O47" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4443,19 +4433,25 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4467,57 +4463,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C48" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D48" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E48" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F48" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H48" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I48" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J48" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K48" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L48" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M48" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N48" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O48" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,25 +4521,21 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4562,50 +4554,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C49" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D49" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E49" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F49" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H49" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I49" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J49" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K49" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L49" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M49" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N49" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O49" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,15 +4608,13 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4639,57 +4629,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C50" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D50" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E50" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F50" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H50" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I50" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J50" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K50" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L50" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M50" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N50" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O50" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4697,12 +4687,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4721,57 +4713,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C51" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D51" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E51" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F51" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H51" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I51" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J51" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K51" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L51" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M51" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N51" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O51" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,14 +4771,12 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4805,57 +4795,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C52" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D52" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E52" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F52" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H52" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I52" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J52" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K52" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L52" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M52" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N52" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O52" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4866,13 +4856,15 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4887,76 +4879,78 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3920.27</v>
+        <v>3878.41</v>
       </c>
       <c r="C53" t="n">
-        <v>3967.68</v>
+        <v>3878.41</v>
       </c>
       <c r="D53" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E53" t="n">
-        <v>3888.37</v>
+        <v>3842.2</v>
       </c>
       <c r="F53" t="n">
-        <v>-23.5</v>
+        <v>-46.18</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0119</v>
       </c>
       <c r="H53" t="n">
-        <v>79.31</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>3765.77</v>
+        <v>3809.07</v>
       </c>
       <c r="J53" t="n">
-        <v>3850.26</v>
+        <v>3789.24</v>
       </c>
       <c r="K53" t="n">
-        <v>3873.4</v>
+        <v>3848.72</v>
       </c>
       <c r="L53" t="n">
-        <v>3896.53</v>
+        <v>3908.2</v>
       </c>
       <c r="M53" t="n">
-        <v>3950.35</v>
+        <v>3928.03</v>
       </c>
       <c r="N53" t="n">
-        <v>4004.16</v>
+        <v>3947.85</v>
       </c>
       <c r="O53" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
+        <v>4046.99</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4971,65 +4965,65 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3878.41</v>
+        <v>3838.98</v>
       </c>
       <c r="C54" t="n">
-        <v>3878.41</v>
+        <v>3864.12</v>
       </c>
       <c r="D54" t="n">
-        <v>3806.67</v>
+        <v>3754.14</v>
       </c>
       <c r="E54" t="n">
-        <v>3842.2</v>
+        <v>3813.79</v>
       </c>
       <c r="F54" t="n">
-        <v>-46.18</v>
+        <v>-28.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0074</v>
       </c>
       <c r="H54" t="n">
-        <v>71.73999999999999</v>
+        <v>109.98</v>
       </c>
       <c r="I54" t="n">
-        <v>3809.07</v>
+        <v>3734.93</v>
       </c>
       <c r="J54" t="n">
-        <v>3789.24</v>
+        <v>3770.28</v>
       </c>
       <c r="K54" t="n">
-        <v>3848.72</v>
+        <v>3806.33</v>
       </c>
       <c r="L54" t="n">
-        <v>3908.2</v>
+        <v>3842.37</v>
       </c>
       <c r="M54" t="n">
-        <v>3928.03</v>
+        <v>3878.06</v>
       </c>
       <c r="N54" t="n">
-        <v>3947.85</v>
+        <v>3913.76</v>
       </c>
       <c r="O54" t="n">
-        <v>4046.99</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>3950.15</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5064,62 +5058,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3838.98</v>
+        <v>3806.98</v>
       </c>
       <c r="C55" t="n">
-        <v>3864.12</v>
+        <v>3828.22</v>
       </c>
       <c r="D55" t="n">
-        <v>3754.14</v>
+        <v>3674.82</v>
       </c>
       <c r="E55" t="n">
-        <v>3813.79</v>
+        <v>3716.28</v>
       </c>
       <c r="F55" t="n">
-        <v>-28.4</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0256</v>
       </c>
       <c r="H55" t="n">
-        <v>109.98</v>
+        <v>153.4</v>
       </c>
       <c r="I55" t="n">
-        <v>3734.93</v>
+        <v>3644.15</v>
       </c>
       <c r="J55" t="n">
-        <v>3770.28</v>
+        <v>3706.14</v>
       </c>
       <c r="K55" t="n">
-        <v>3806.33</v>
+        <v>3758.8</v>
       </c>
       <c r="L55" t="n">
-        <v>3842.37</v>
+        <v>3811.46</v>
       </c>
       <c r="M55" t="n">
-        <v>3878.06</v>
+        <v>3868.78</v>
       </c>
       <c r="N55" t="n">
-        <v>3913.76</v>
+        <v>3926.11</v>
       </c>
       <c r="O55" t="n">
-        <v>3950.15</v>
+        <v>3974.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5150,58 +5144,56 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3806.98</v>
+        <v>3694.12</v>
       </c>
       <c r="C56" t="n">
-        <v>3828.22</v>
+        <v>3743.8</v>
       </c>
       <c r="D56" t="n">
-        <v>3674.82</v>
+        <v>3574.27</v>
       </c>
       <c r="E56" t="n">
-        <v>3716.28</v>
+        <v>3690.48</v>
       </c>
       <c r="F56" t="n">
-        <v>-97.51000000000001</v>
+        <v>-25.81</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.0069</v>
       </c>
       <c r="H56" t="n">
-        <v>153.4</v>
+        <v>169.53</v>
       </c>
       <c r="I56" t="n">
-        <v>3644.15</v>
+        <v>3521.42</v>
       </c>
       <c r="J56" t="n">
-        <v>3706.14</v>
+        <v>3545.27</v>
       </c>
       <c r="K56" t="n">
-        <v>3758.8</v>
+        <v>3639.58</v>
       </c>
       <c r="L56" t="n">
-        <v>3811.46</v>
+        <v>3733.9</v>
       </c>
       <c r="M56" t="n">
-        <v>3868.78</v>
+        <v>3792.98</v>
       </c>
       <c r="N56" t="n">
-        <v>3926.11</v>
+        <v>3852.07</v>
       </c>
       <c r="O56" t="n">
-        <v>3974.1</v>
+        <v>3981.62</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5210,7 +5202,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5228,90 +5220,6 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3694.12</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3743.8</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3649.86</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3658.03</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-58.26</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0157</v>
-      </c>
-      <c r="H57" t="n">
-        <v>93.93000000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3521.42</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3545.27</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3639.58</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3733.9</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3792.98</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3852.07</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3981.62</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5225,6 +5225,88 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3671</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3699.01</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3664.82</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3697.52</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="H57" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3404.74</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3536.67</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3605.71</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3674.76</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3775.24</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3875.72</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3913.33</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>78.04000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3682.95</v>
+        <v>3742.55</v>
       </c>
       <c r="J2" t="n">
-        <v>3740.42</v>
+        <v>3762.77</v>
       </c>
       <c r="K2" t="n">
-        <v>3782.32</v>
+        <v>3797.22</v>
       </c>
       <c r="L2" t="n">
-        <v>3824.21</v>
+        <v>3831.66</v>
       </c>
       <c r="M2" t="n">
-        <v>3873.89</v>
+        <v>3858.99</v>
       </c>
       <c r="N2" t="n">
-        <v>3923.58</v>
+        <v>3886.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3957.68</v>
+        <v>3927.88</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5235,22 +5237,22 @@
         <v>3671</v>
       </c>
       <c r="C57" t="n">
-        <v>3699.01</v>
+        <v>3708.2</v>
       </c>
       <c r="D57" t="n">
-        <v>3664.82</v>
+        <v>3648.3</v>
       </c>
       <c r="E57" t="n">
-        <v>3697.52</v>
+        <v>3648.3</v>
       </c>
       <c r="F57" t="n">
-        <v>7.04</v>
+        <v>-42.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0114</v>
       </c>
       <c r="H57" t="n">
-        <v>34.19</v>
+        <v>59.9</v>
       </c>
       <c r="I57" t="n">
         <v>3404.74</v>
@@ -5282,9 +5284,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5303,7 +5305,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>78.04000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3742.55</v>
+        <v>3790.11</v>
       </c>
       <c r="J2" t="n">
-        <v>3762.77</v>
+        <v>3780.61</v>
       </c>
       <c r="K2" t="n">
-        <v>3797.22</v>
+        <v>3809.11</v>
       </c>
       <c r="L2" t="n">
-        <v>3831.66</v>
+        <v>3837.61</v>
       </c>
       <c r="M2" t="n">
-        <v>3858.99</v>
+        <v>3847.11</v>
       </c>
       <c r="N2" t="n">
-        <v>3886.33</v>
+        <v>3856.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3927.88</v>
+        <v>3904.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,18 +700,24 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5243,13 +5249,13 @@
         <v>3648.3</v>
       </c>
       <c r="E57" t="n">
-        <v>3648.3</v>
+        <v>3681.47</v>
       </c>
       <c r="F57" t="n">
-        <v>-42.17</v>
+        <v>-9.01</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0024</v>
       </c>
       <c r="H57" t="n">
         <v>59.9</v>
@@ -5284,9 +5290,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>78.04000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3790.11</v>
+        <v>3799.61</v>
       </c>
       <c r="J2" t="n">
-        <v>3780.61</v>
+        <v>3792.48</v>
       </c>
       <c r="K2" t="n">
-        <v>3809.11</v>
+        <v>3813.86</v>
       </c>
       <c r="L2" t="n">
-        <v>3837.61</v>
+        <v>3835.23</v>
       </c>
       <c r="M2" t="n">
-        <v>3847.11</v>
+        <v>3842.36</v>
       </c>
       <c r="N2" t="n">
-        <v>3856.61</v>
+        <v>3849.48</v>
       </c>
       <c r="O2" t="n">
-        <v>3904.11</v>
+        <v>3885.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5246,19 +5248,19 @@
         <v>3708.2</v>
       </c>
       <c r="D57" t="n">
-        <v>3648.3</v>
+        <v>3645.26</v>
       </c>
       <c r="E57" t="n">
-        <v>3681.47</v>
+        <v>3651.43</v>
       </c>
       <c r="F57" t="n">
-        <v>-9.01</v>
+        <v>-39.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0106</v>
       </c>
       <c r="H57" t="n">
-        <v>59.9</v>
+        <v>62.94</v>
       </c>
       <c r="I57" t="n">
         <v>3404.74</v>
@@ -5290,9 +5292,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/SSE_weekly.xlsx
+++ b/three_gate/analysis/SSE_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3828.17</v>
+        <v>3898.31</v>
       </c>
       <c r="C2" t="n">
-        <v>3887.57</v>
+        <v>3936.58</v>
       </c>
       <c r="D2" t="n">
-        <v>3809.53</v>
+        <v>3885.74</v>
       </c>
       <c r="E2" t="n">
-        <v>3882.78</v>
+        <v>3897.03</v>
       </c>
       <c r="F2" t="n">
-        <v>54.67</v>
+        <v>14.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0037</v>
       </c>
       <c r="H2" t="n">
-        <v>78.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I2" t="n">
-        <v>3799.61</v>
+        <v>3731.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3792.48</v>
+        <v>3821.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3813.86</v>
+        <v>3843.76</v>
       </c>
       <c r="L2" t="n">
-        <v>3835.23</v>
+        <v>3865.66</v>
       </c>
       <c r="M2" t="n">
-        <v>3842.36</v>
+        <v>3921.79</v>
       </c>
       <c r="N2" t="n">
-        <v>3849.48</v>
+        <v>3977.92</v>
       </c>
       <c r="O2" t="n">
-        <v>3885.11</v>
+        <v>3965.61</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -697,95 +695,93 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3898.31</v>
+        <v>3800.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3936.58</v>
+        <v>3931.05</v>
       </c>
       <c r="D3" t="n">
-        <v>3885.74</v>
+        <v>3800.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3897.03</v>
+        <v>3839.75</v>
       </c>
       <c r="F3" t="n">
-        <v>14.25</v>
+        <v>-57.27</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0147</v>
       </c>
       <c r="H3" t="n">
-        <v>50.83</v>
+        <v>130.95</v>
       </c>
       <c r="I3" t="n">
-        <v>3731.5</v>
+        <v>3834.91</v>
       </c>
       <c r="J3" t="n">
-        <v>3821.85</v>
+        <v>3839.13</v>
       </c>
       <c r="K3" t="n">
-        <v>3843.76</v>
+        <v>3871.61</v>
       </c>
       <c r="L3" t="n">
-        <v>3865.66</v>
+        <v>3904.09</v>
       </c>
       <c r="M3" t="n">
-        <v>3921.79</v>
+        <v>3922.44</v>
       </c>
       <c r="N3" t="n">
-        <v>3977.92</v>
+        <v>3940.79</v>
       </c>
       <c r="O3" t="n">
-        <v>3965.61</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>3987.41</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -799,84 +795,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3800.1</v>
+        <v>3865.55</v>
       </c>
       <c r="C4" t="n">
-        <v>3931.05</v>
+        <v>3950.31</v>
       </c>
       <c r="D4" t="n">
-        <v>3800.1</v>
+        <v>3850.37</v>
       </c>
       <c r="E4" t="n">
-        <v>3839.75</v>
+        <v>3950.31</v>
       </c>
       <c r="F4" t="n">
-        <v>-57.27</v>
+        <v>110.56</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0288</v>
       </c>
       <c r="H4" t="n">
-        <v>130.95</v>
+        <v>99.95</v>
       </c>
       <c r="I4" t="n">
-        <v>3834.91</v>
+        <v>3669.16</v>
       </c>
       <c r="J4" t="n">
-        <v>3839.13</v>
+        <v>3695.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3871.61</v>
+        <v>3774.28</v>
       </c>
       <c r="L4" t="n">
-        <v>3904.09</v>
+        <v>3852.67</v>
       </c>
       <c r="M4" t="n">
-        <v>3922.44</v>
+        <v>3905.23</v>
       </c>
       <c r="N4" t="n">
-        <v>3940.79</v>
+        <v>3957.79</v>
       </c>
       <c r="O4" t="n">
-        <v>3987.41</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>4062</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -885,59 +881,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3865.55</v>
+        <v>3969.22</v>
       </c>
       <c r="C5" t="n">
-        <v>3950.31</v>
+        <v>4025.71</v>
       </c>
       <c r="D5" t="n">
-        <v>3850.37</v>
+        <v>3951.73</v>
       </c>
       <c r="E5" t="n">
-        <v>3950.31</v>
+        <v>3954.79</v>
       </c>
       <c r="F5" t="n">
-        <v>110.56</v>
+        <v>4.48</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0011</v>
       </c>
       <c r="H5" t="n">
-        <v>99.95</v>
+        <v>73.97</v>
       </c>
       <c r="I5" t="n">
-        <v>3669.16</v>
+        <v>3750.42</v>
       </c>
       <c r="J5" t="n">
-        <v>3695.9</v>
+        <v>3875.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3774.28</v>
+        <v>3900.34</v>
       </c>
       <c r="L5" t="n">
-        <v>3852.67</v>
+        <v>3925.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3905.23</v>
+        <v>4000.28</v>
       </c>
       <c r="N5" t="n">
-        <v>3957.79</v>
+        <v>4075.24</v>
       </c>
       <c r="O5" t="n">
-        <v>4062</v>
+        <v>4050.26</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -950,7 +942,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -958,10 +950,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -976,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3969.22</v>
+        <v>3954.08</v>
       </c>
       <c r="C6" t="n">
-        <v>4025.71</v>
+        <v>4012</v>
       </c>
       <c r="D6" t="n">
-        <v>3951.73</v>
+        <v>3922.58</v>
       </c>
       <c r="E6" t="n">
-        <v>3954.79</v>
+        <v>3997.56</v>
       </c>
       <c r="F6" t="n">
-        <v>4.48</v>
+        <v>42.77</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0108</v>
       </c>
       <c r="H6" t="n">
-        <v>73.97</v>
+        <v>89.42</v>
       </c>
       <c r="I6" t="n">
-        <v>3750.42</v>
+        <v>3877.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3875.35</v>
+        <v>3863.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3900.34</v>
+        <v>3917.8</v>
       </c>
       <c r="L6" t="n">
-        <v>3925.33</v>
+        <v>3971.75</v>
       </c>
       <c r="M6" t="n">
-        <v>4000.28</v>
+        <v>3991.78</v>
       </c>
       <c r="N6" t="n">
-        <v>4075.24</v>
+        <v>4011.8</v>
       </c>
       <c r="O6" t="n">
-        <v>4050.26</v>
+        <v>4099.68</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1032,17 +1022,19 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1051,55 +1043,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3954.08</v>
+        <v>4001.79</v>
       </c>
       <c r="C7" t="n">
-        <v>4012</v>
+        <v>4034.08</v>
       </c>
       <c r="D7" t="n">
-        <v>3922.58</v>
+        <v>3980.68</v>
       </c>
       <c r="E7" t="n">
-        <v>3997.56</v>
+        <v>3990.49</v>
       </c>
       <c r="F7" t="n">
-        <v>42.77</v>
+        <v>-7.06</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0108</v>
+        <v>-0.0018</v>
       </c>
       <c r="H7" t="n">
-        <v>89.42</v>
+        <v>53.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3877.76</v>
+        <v>3833.16</v>
       </c>
       <c r="J7" t="n">
-        <v>3863.85</v>
+        <v>3923.27</v>
       </c>
       <c r="K7" t="n">
-        <v>3917.8</v>
+        <v>3952.85</v>
       </c>
       <c r="L7" t="n">
-        <v>3971.75</v>
+        <v>3982.43</v>
       </c>
       <c r="M7" t="n">
-        <v>3991.78</v>
+        <v>4042.27</v>
       </c>
       <c r="N7" t="n">
-        <v>4011.8</v>
+        <v>4102.11</v>
       </c>
       <c r="O7" t="n">
-        <v>4099.68</v>
+        <v>4101.43</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,18 +1108,14 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1135,70 +1127,76 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4001.79</v>
+        <v>3988.56</v>
       </c>
       <c r="C8" t="n">
-        <v>4034.08</v>
+        <v>3992.4</v>
       </c>
       <c r="D8" t="n">
-        <v>3980.68</v>
+        <v>3834.75</v>
       </c>
       <c r="E8" t="n">
-        <v>3990.49</v>
+        <v>3834.89</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.06</v>
+        <v>-155.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.039</v>
       </c>
       <c r="H8" t="n">
-        <v>53.4</v>
+        <v>157.66</v>
       </c>
       <c r="I8" t="n">
-        <v>3833.16</v>
+        <v>3927.27</v>
       </c>
       <c r="J8" t="n">
-        <v>3923.27</v>
+        <v>3928.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3952.85</v>
+        <v>3963.79</v>
       </c>
       <c r="L8" t="n">
-        <v>3982.43</v>
+        <v>3998.93</v>
       </c>
       <c r="M8" t="n">
-        <v>4042.27</v>
+        <v>4017.19</v>
       </c>
       <c r="N8" t="n">
-        <v>4102.11</v>
+        <v>4035.45</v>
       </c>
       <c r="O8" t="n">
-        <v>4101.43</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4087.48</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1210,83 +1208,73 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3988.56</v>
+        <v>3848.66</v>
       </c>
       <c r="C9" t="n">
-        <v>3992.4</v>
+        <v>3895.59</v>
       </c>
       <c r="D9" t="n">
-        <v>3834.75</v>
+        <v>3816.58</v>
       </c>
       <c r="E9" t="n">
-        <v>3834.89</v>
+        <v>3888.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-155.6</v>
+        <v>53.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.039</v>
+        <v>0.014</v>
       </c>
       <c r="H9" t="n">
-        <v>157.66</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>3927.27</v>
+        <v>3677.09</v>
       </c>
       <c r="J9" t="n">
-        <v>3928.65</v>
+        <v>3637.89</v>
       </c>
       <c r="K9" t="n">
-        <v>3963.79</v>
+        <v>3756.06</v>
       </c>
       <c r="L9" t="n">
-        <v>3998.93</v>
+        <v>3874.23</v>
       </c>
       <c r="M9" t="n">
-        <v>4017.19</v>
+        <v>3913.72</v>
       </c>
       <c r="N9" t="n">
-        <v>4035.45</v>
+        <v>3953.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4087.48</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4150.06</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1303,55 +1291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3848.66</v>
+        <v>3894.21</v>
       </c>
       <c r="C10" t="n">
-        <v>3895.59</v>
+        <v>3914.46</v>
       </c>
       <c r="D10" t="n">
-        <v>3816.58</v>
+        <v>3859.05</v>
       </c>
       <c r="E10" t="n">
-        <v>3888.6</v>
+        <v>3902.81</v>
       </c>
       <c r="F10" t="n">
-        <v>53.7</v>
+        <v>14.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0037</v>
       </c>
       <c r="H10" t="n">
-        <v>79.01000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="I10" t="n">
-        <v>3677.09</v>
+        <v>3737.56</v>
       </c>
       <c r="J10" t="n">
-        <v>3637.89</v>
+        <v>3825.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3756.06</v>
+        <v>3849.09</v>
       </c>
       <c r="L10" t="n">
-        <v>3874.23</v>
+        <v>3872.34</v>
       </c>
       <c r="M10" t="n">
-        <v>3913.72</v>
+        <v>3928.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3953.2</v>
+        <v>3983.87</v>
       </c>
       <c r="O10" t="n">
-        <v>4150.06</v>
+        <v>3974.6</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,11 +1356,13 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1383,75 +1377,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3894.21</v>
+        <v>3909.23</v>
       </c>
       <c r="C11" t="n">
-        <v>3914.46</v>
+        <v>3936.31</v>
       </c>
       <c r="D11" t="n">
-        <v>3859.05</v>
+        <v>3850.6</v>
       </c>
       <c r="E11" t="n">
-        <v>3902.81</v>
+        <v>3889.35</v>
       </c>
       <c r="F11" t="n">
-        <v>14.21</v>
+        <v>-13.46</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0034</v>
       </c>
       <c r="H11" t="n">
-        <v>55.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3737.56</v>
+        <v>3803.63</v>
       </c>
       <c r="J11" t="n">
-        <v>3825.84</v>
+        <v>3855.42</v>
       </c>
       <c r="K11" t="n">
-        <v>3849.09</v>
+        <v>3875.1</v>
       </c>
       <c r="L11" t="n">
-        <v>3872.34</v>
+        <v>3894.78</v>
       </c>
       <c r="M11" t="n">
-        <v>3928.1</v>
+        <v>3930.52</v>
       </c>
       <c r="N11" t="n">
-        <v>3983.87</v>
+        <v>3966.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3974.6</v>
+        <v>3969.88</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1467,80 +1465,76 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3909.23</v>
+        <v>3865.4</v>
       </c>
       <c r="C12" t="n">
-        <v>3936.31</v>
+        <v>3902.67</v>
       </c>
       <c r="D12" t="n">
-        <v>3850.6</v>
+        <v>3815.84</v>
       </c>
       <c r="E12" t="n">
-        <v>3889.35</v>
+        <v>3890.45</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.46</v>
+        <v>1.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="I12" t="n">
-        <v>3803.63</v>
+        <v>3764.88</v>
       </c>
       <c r="J12" t="n">
-        <v>3855.42</v>
+        <v>3801.58</v>
       </c>
       <c r="K12" t="n">
-        <v>3875.1</v>
+        <v>3846.49</v>
       </c>
       <c r="L12" t="n">
-        <v>3894.78</v>
+        <v>3891.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3930.52</v>
+        <v>3932.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3966.25</v>
+        <v>3973.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3969.88</v>
+        <v>4022.03</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1562,50 +1556,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3865.4</v>
+        <v>3900.53</v>
       </c>
       <c r="C13" t="n">
-        <v>3902.67</v>
+        <v>3977.71</v>
       </c>
       <c r="D13" t="n">
-        <v>3815.84</v>
+        <v>3900.51</v>
       </c>
       <c r="E13" t="n">
-        <v>3890.45</v>
+        <v>3963.68</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>73.23</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0188</v>
       </c>
       <c r="H13" t="n">
-        <v>86.83</v>
+        <v>77.19</v>
       </c>
       <c r="I13" t="n">
-        <v>3764.88</v>
+        <v>3729.02</v>
       </c>
       <c r="J13" t="n">
-        <v>3801.58</v>
+        <v>3819.22</v>
       </c>
       <c r="K13" t="n">
-        <v>3846.49</v>
+        <v>3847.03</v>
       </c>
       <c r="L13" t="n">
-        <v>3891.4</v>
+        <v>3874.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3932.2</v>
+        <v>3933.86</v>
       </c>
       <c r="N13" t="n">
-        <v>3973.01</v>
+        <v>3992.87</v>
       </c>
       <c r="O13" t="n">
-        <v>4022.03</v>
+        <v>3989.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1613,24 +1607,26 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
@@ -1639,57 +1635,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3900.53</v>
+        <v>3964.65</v>
       </c>
       <c r="C14" t="n">
-        <v>3977.71</v>
+        <v>3983.98</v>
       </c>
       <c r="D14" t="n">
-        <v>3900.51</v>
+        <v>3947.42</v>
       </c>
       <c r="E14" t="n">
-        <v>3963.68</v>
+        <v>3968.84</v>
       </c>
       <c r="F14" t="n">
-        <v>73.23</v>
+        <v>5.16</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0013</v>
       </c>
       <c r="H14" t="n">
-        <v>77.19</v>
+        <v>36.56</v>
       </c>
       <c r="I14" t="n">
-        <v>3729.02</v>
+        <v>3823.32</v>
       </c>
       <c r="J14" t="n">
-        <v>3819.22</v>
+        <v>3898.77</v>
       </c>
       <c r="K14" t="n">
-        <v>3847.03</v>
+        <v>3925.08</v>
       </c>
       <c r="L14" t="n">
-        <v>3874.85</v>
+        <v>3951.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3933.86</v>
+        <v>4002.27</v>
       </c>
       <c r="N14" t="n">
-        <v>3992.87</v>
+        <v>4053.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3989.5</v>
+        <v>4054.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1702,21 +1698,17 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1732,50 +1724,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3964.65</v>
+        <v>3986.97</v>
       </c>
       <c r="C15" t="n">
-        <v>3983.98</v>
+        <v>4121.72</v>
       </c>
       <c r="D15" t="n">
-        <v>3947.42</v>
+        <v>3983.58</v>
       </c>
       <c r="E15" t="n">
-        <v>3968.84</v>
+        <v>4120.43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.16</v>
+        <v>151.59</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0382</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56</v>
+        <v>138.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3823.32</v>
+        <v>3910.86</v>
       </c>
       <c r="J15" t="n">
-        <v>3898.77</v>
+        <v>3933.85</v>
       </c>
       <c r="K15" t="n">
-        <v>3925.08</v>
+        <v>3950.56</v>
       </c>
       <c r="L15" t="n">
-        <v>3951.39</v>
+        <v>3967.27</v>
       </c>
       <c r="M15" t="n">
-        <v>4002.27</v>
+        <v>3987.12</v>
       </c>
       <c r="N15" t="n">
-        <v>4053.15</v>
+        <v>4006.97</v>
       </c>
       <c r="O15" t="n">
-        <v>4054.9</v>
+        <v>4020.54</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1788,76 +1780,78 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3986.97</v>
+        <v>4134.89</v>
       </c>
       <c r="C16" t="n">
-        <v>4121.72</v>
+        <v>4190.87</v>
       </c>
       <c r="D16" t="n">
-        <v>3983.58</v>
+        <v>4091.81</v>
       </c>
       <c r="E16" t="n">
-        <v>4120.43</v>
+        <v>4101.91</v>
       </c>
       <c r="F16" t="n">
-        <v>151.59</v>
+        <v>-18.51</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0382</v>
+        <v>-0.0045</v>
       </c>
       <c r="H16" t="n">
-        <v>138.15</v>
+        <v>99.06</v>
       </c>
       <c r="I16" t="n">
-        <v>3910.86</v>
+        <v>3845.43</v>
       </c>
       <c r="J16" t="n">
-        <v>3933.85</v>
+        <v>4016.17</v>
       </c>
       <c r="K16" t="n">
-        <v>3950.56</v>
+        <v>4051.35</v>
       </c>
       <c r="L16" t="n">
-        <v>3967.27</v>
+        <v>4086.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3987.12</v>
+        <v>4189.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4006.97</v>
+        <v>4292.46</v>
       </c>
       <c r="O16" t="n">
-        <v>4020.54</v>
+        <v>4259.87</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1870,7 +1864,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1878,70 +1872,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4134.89</v>
+        <v>4090.72</v>
       </c>
       <c r="C17" t="n">
-        <v>4190.87</v>
+        <v>4143.75</v>
       </c>
       <c r="D17" t="n">
-        <v>4091.81</v>
+        <v>4080.29</v>
       </c>
       <c r="E17" t="n">
-        <v>4101.91</v>
+        <v>4136.16</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.51</v>
+        <v>34.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>99.06</v>
+        <v>63.46</v>
       </c>
       <c r="I17" t="n">
-        <v>3845.43</v>
+        <v>3992.76</v>
       </c>
       <c r="J17" t="n">
-        <v>4016.17</v>
+        <v>3983.15</v>
       </c>
       <c r="K17" t="n">
-        <v>4051.35</v>
+        <v>4052.39</v>
       </c>
       <c r="L17" t="n">
-        <v>4086.54</v>
+        <v>4121.63</v>
       </c>
       <c r="M17" t="n">
-        <v>4189.5</v>
+        <v>4151.44</v>
       </c>
       <c r="N17" t="n">
-        <v>4292.46</v>
+        <v>4181.26</v>
       </c>
       <c r="O17" t="n">
-        <v>4259.87</v>
+        <v>4289.92</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1957,10 +1951,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1975,74 +1967,80 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4090.72</v>
+        <v>4144.78</v>
       </c>
       <c r="C18" t="n">
-        <v>4143.75</v>
+        <v>4170.21</v>
       </c>
       <c r="D18" t="n">
-        <v>4080.29</v>
+        <v>4064.78</v>
       </c>
       <c r="E18" t="n">
-        <v>4136.16</v>
+        <v>4117.95</v>
       </c>
       <c r="F18" t="n">
-        <v>34.25</v>
+        <v>-18.22</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="H18" t="n">
-        <v>63.46</v>
+        <v>105.44</v>
       </c>
       <c r="I18" t="n">
-        <v>3992.76</v>
+        <v>4016.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3983.15</v>
+        <v>4084.78</v>
       </c>
       <c r="K18" t="n">
-        <v>4052.39</v>
+        <v>4104.44</v>
       </c>
       <c r="L18" t="n">
-        <v>4121.63</v>
+        <v>4124.09</v>
       </c>
       <c r="M18" t="n">
-        <v>4151.44</v>
+        <v>4167.89</v>
       </c>
       <c r="N18" t="n">
-        <v>4181.26</v>
+        <v>4211.69</v>
       </c>
       <c r="O18" t="n">
-        <v>4289.92</v>
+        <v>4207.21</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2064,50 +2062,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4144.78</v>
+        <v>4079.71</v>
       </c>
       <c r="C19" t="n">
-        <v>4170.21</v>
+        <v>4104.62</v>
       </c>
       <c r="D19" t="n">
-        <v>4064.78</v>
+        <v>4002.78</v>
       </c>
       <c r="E19" t="n">
-        <v>4117.95</v>
+        <v>4065.58</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.22</v>
+        <v>-52.37</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0127</v>
       </c>
       <c r="H19" t="n">
-        <v>105.44</v>
+        <v>101.84</v>
       </c>
       <c r="I19" t="n">
-        <v>4016.84</v>
+        <v>3959.34</v>
       </c>
       <c r="J19" t="n">
-        <v>4084.78</v>
+        <v>4012.74</v>
       </c>
       <c r="K19" t="n">
-        <v>4104.44</v>
+        <v>4065.23</v>
       </c>
       <c r="L19" t="n">
-        <v>4124.09</v>
+        <v>4117.72</v>
       </c>
       <c r="M19" t="n">
-        <v>4167.89</v>
+        <v>4170.67</v>
       </c>
       <c r="N19" t="n">
-        <v>4211.69</v>
+        <v>4223.61</v>
       </c>
       <c r="O19" t="n">
-        <v>4207.21</v>
+        <v>4275.65</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,18 +2117,16 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2145,79 +2141,77 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4079.71</v>
+        <v>4103.54</v>
       </c>
       <c r="C20" t="n">
-        <v>4104.62</v>
+        <v>4142.56</v>
       </c>
       <c r="D20" t="n">
-        <v>4002.78</v>
+        <v>4079.77</v>
       </c>
       <c r="E20" t="n">
-        <v>4065.58</v>
+        <v>4082.07</v>
       </c>
       <c r="F20" t="n">
-        <v>-52.37</v>
+        <v>16.49</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0041</v>
       </c>
       <c r="H20" t="n">
-        <v>101.84</v>
+        <v>62.79</v>
       </c>
       <c r="I20" t="n">
-        <v>3959.34</v>
+        <v>3900.94</v>
       </c>
       <c r="J20" t="n">
-        <v>4012.74</v>
+        <v>3969.68</v>
       </c>
       <c r="K20" t="n">
-        <v>4065.23</v>
+        <v>4014.66</v>
       </c>
       <c r="L20" t="n">
-        <v>4117.72</v>
+        <v>4059.64</v>
       </c>
       <c r="M20" t="n">
-        <v>4170.67</v>
+        <v>4116.5</v>
       </c>
       <c r="N20" t="n">
-        <v>4223.61</v>
+        <v>4173.36</v>
       </c>
       <c r="O20" t="n">
-        <v>4275.65</v>
+        <v>4206.46</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2229,59 +2223,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4103.54</v>
+        <v>4129.13</v>
       </c>
       <c r="C21" t="n">
-        <v>4142.56</v>
+        <v>4167.84</v>
       </c>
       <c r="D21" t="n">
-        <v>4079.77</v>
+        <v>4105.94</v>
       </c>
       <c r="E21" t="n">
-        <v>4082.07</v>
+        <v>4162.88</v>
       </c>
       <c r="F21" t="n">
-        <v>16.49</v>
+        <v>80.81</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0198</v>
       </c>
       <c r="H21" t="n">
-        <v>62.79</v>
+        <v>61.91</v>
       </c>
       <c r="I21" t="n">
-        <v>3900.94</v>
+        <v>4016.98</v>
       </c>
       <c r="J21" t="n">
-        <v>3969.68</v>
+        <v>4004.74</v>
       </c>
       <c r="K21" t="n">
-        <v>4014.66</v>
+        <v>4050.68</v>
       </c>
       <c r="L21" t="n">
-        <v>4059.64</v>
+        <v>4096.62</v>
       </c>
       <c r="M21" t="n">
-        <v>4116.5</v>
+        <v>4113.47</v>
       </c>
       <c r="N21" t="n">
-        <v>4173.36</v>
+        <v>4130.32</v>
       </c>
       <c r="O21" t="n">
-        <v>4206.46</v>
+        <v>4205.35</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2294,7 +2284,7 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2302,8 +2292,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2318,63 +2310,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4129.13</v>
+        <v>4151.8</v>
       </c>
       <c r="C22" t="n">
-        <v>4167.84</v>
+        <v>4197.23</v>
       </c>
       <c r="D22" t="n">
-        <v>4105.94</v>
+        <v>4055.41</v>
       </c>
       <c r="E22" t="n">
-        <v>4162.88</v>
+        <v>4124.19</v>
       </c>
       <c r="F22" t="n">
-        <v>80.81</v>
+        <v>-38.69</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0198</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>61.91</v>
+        <v>141.81</v>
       </c>
       <c r="I22" t="n">
-        <v>4016.98</v>
+        <v>4044.03</v>
       </c>
       <c r="J22" t="n">
-        <v>4004.74</v>
+        <v>4113.97</v>
       </c>
       <c r="K22" t="n">
-        <v>4050.68</v>
+        <v>4131.93</v>
       </c>
       <c r="L22" t="n">
-        <v>4096.62</v>
+        <v>4149.89</v>
       </c>
       <c r="M22" t="n">
-        <v>4113.47</v>
+        <v>4193.83</v>
       </c>
       <c r="N22" t="n">
-        <v>4130.32</v>
+        <v>4237.78</v>
       </c>
       <c r="O22" t="n">
-        <v>4205.35</v>
+        <v>4229.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2382,10 +2378,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2395,78 +2389,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4151.8</v>
+        <v>4098.7</v>
       </c>
       <c r="C23" t="n">
-        <v>4197.23</v>
+        <v>4141.65</v>
       </c>
       <c r="D23" t="n">
-        <v>4055.41</v>
+        <v>4052.54</v>
       </c>
       <c r="E23" t="n">
-        <v>4124.19</v>
+        <v>4095.45</v>
       </c>
       <c r="F23" t="n">
-        <v>-38.69</v>
+        <v>-28.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H23" t="n">
-        <v>141.81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>4044.03</v>
+        <v>3913.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4113.97</v>
+        <v>3981.32</v>
       </c>
       <c r="K23" t="n">
-        <v>4131.93</v>
+        <v>4053.29</v>
       </c>
       <c r="L23" t="n">
-        <v>4149.89</v>
+        <v>4125.26</v>
       </c>
       <c r="M23" t="n">
-        <v>4193.83</v>
+        <v>4195.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4237.78</v>
+        <v>4264.95</v>
       </c>
       <c r="O23" t="n">
-        <v>4229.75</v>
+        <v>4339.04</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2481,63 +2475,67 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4098.7</v>
+        <v>4092.25</v>
       </c>
       <c r="C24" t="n">
-        <v>4141.65</v>
+        <v>4108.4</v>
       </c>
       <c r="D24" t="n">
-        <v>4052.54</v>
+        <v>3955.71</v>
       </c>
       <c r="E24" t="n">
-        <v>4095.45</v>
+        <v>3957.05</v>
       </c>
       <c r="F24" t="n">
-        <v>-28.75</v>
+        <v>-138.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0338</v>
       </c>
       <c r="H24" t="n">
-        <v>89.09999999999999</v>
+        <v>152.69</v>
       </c>
       <c r="I24" t="n">
-        <v>3913.6</v>
+        <v>3963.44</v>
       </c>
       <c r="J24" t="n">
-        <v>3981.32</v>
+        <v>4005.52</v>
       </c>
       <c r="K24" t="n">
-        <v>4053.29</v>
+        <v>4050.9</v>
       </c>
       <c r="L24" t="n">
-        <v>4125.26</v>
+        <v>4096.27</v>
       </c>
       <c r="M24" t="n">
-        <v>4195.1</v>
+        <v>4140</v>
       </c>
       <c r="N24" t="n">
-        <v>4264.95</v>
+        <v>4183.73</v>
       </c>
       <c r="O24" t="n">
-        <v>4339.04</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>4230.75</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
@@ -2546,7 +2544,7 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2558,78 +2556,72 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4092.25</v>
+        <v>3904.95</v>
       </c>
       <c r="C25" t="n">
-        <v>4108.4</v>
+        <v>3937.1</v>
       </c>
       <c r="D25" t="n">
-        <v>3955.71</v>
+        <v>3794.68</v>
       </c>
       <c r="E25" t="n">
-        <v>3957.05</v>
+        <v>3913.72</v>
       </c>
       <c r="F25" t="n">
-        <v>-138.4</v>
+        <v>-43.33</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0338</v>
+        <v>-0.0109</v>
       </c>
       <c r="H25" t="n">
-        <v>152.69</v>
+        <v>142.42</v>
       </c>
       <c r="I25" t="n">
-        <v>3963.44</v>
+        <v>3803.02</v>
       </c>
       <c r="J25" t="n">
-        <v>4005.52</v>
+        <v>3766.86</v>
       </c>
       <c r="K25" t="n">
-        <v>4050.9</v>
+        <v>3880.71</v>
       </c>
       <c r="L25" t="n">
-        <v>4096.27</v>
+        <v>3994.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4140</v>
+        <v>4033.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4183.73</v>
+        <v>4072.24</v>
       </c>
       <c r="O25" t="n">
-        <v>4230.75</v>
+        <v>4261.09</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
@@ -2656,67 +2648,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3904.95</v>
+        <v>3884.28</v>
       </c>
       <c r="C26" t="n">
-        <v>3937.1</v>
+        <v>3955.94</v>
       </c>
       <c r="D26" t="n">
-        <v>3794.68</v>
+        <v>3871.3</v>
       </c>
       <c r="E26" t="n">
-        <v>3913.72</v>
+        <v>3880.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-43.33</v>
+        <v>-33.63</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0086</v>
       </c>
       <c r="H26" t="n">
-        <v>142.42</v>
+        <v>84.64</v>
       </c>
       <c r="I26" t="n">
-        <v>3803.02</v>
+        <v>3652.26</v>
       </c>
       <c r="J26" t="n">
-        <v>3766.86</v>
+        <v>3795.22</v>
       </c>
       <c r="K26" t="n">
-        <v>3880.71</v>
+        <v>3842.51</v>
       </c>
       <c r="L26" t="n">
-        <v>3994.55</v>
+        <v>3889.81</v>
       </c>
       <c r="M26" t="n">
-        <v>4033.4</v>
+        <v>3984.93</v>
       </c>
       <c r="N26" t="n">
-        <v>4072.24</v>
+        <v>4080.06</v>
       </c>
       <c r="O26" t="n">
-        <v>4261.09</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4079.52</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
       </c>
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2733,55 +2721,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3884.28</v>
+        <v>3884.15</v>
       </c>
       <c r="C27" t="n">
-        <v>3955.94</v>
+        <v>4011.02</v>
       </c>
       <c r="D27" t="n">
-        <v>3871.3</v>
+        <v>3875.68</v>
       </c>
       <c r="E27" t="n">
-        <v>3880.1</v>
+        <v>3986.23</v>
       </c>
       <c r="F27" t="n">
-        <v>-33.63</v>
+        <v>106.13</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0274</v>
       </c>
       <c r="H27" t="n">
-        <v>84.64</v>
+        <v>135.34</v>
       </c>
       <c r="I27" t="n">
-        <v>3652.26</v>
+        <v>3786.66</v>
       </c>
       <c r="J27" t="n">
-        <v>3795.22</v>
+        <v>3778.69</v>
       </c>
       <c r="K27" t="n">
-        <v>3842.51</v>
+        <v>3837.78</v>
       </c>
       <c r="L27" t="n">
-        <v>3889.81</v>
+        <v>3896.86</v>
       </c>
       <c r="M27" t="n">
-        <v>3984.93</v>
+        <v>3922.42</v>
       </c>
       <c r="N27" t="n">
-        <v>4080.06</v>
+        <v>3947.98</v>
       </c>
       <c r="O27" t="n">
-        <v>4079.52</v>
+        <v>4040.59</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2792,78 +2784,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3884.15</v>
+        <v>3971.2</v>
       </c>
       <c r="C28" t="n">
-        <v>4011.02</v>
+        <v>4058.6</v>
       </c>
       <c r="D28" t="n">
-        <v>3875.68</v>
+        <v>3966.2</v>
       </c>
       <c r="E28" t="n">
-        <v>3986.23</v>
+        <v>4051.43</v>
       </c>
       <c r="F28" t="n">
-        <v>106.13</v>
+        <v>65.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0164</v>
       </c>
       <c r="H28" t="n">
-        <v>135.34</v>
+        <v>92.41</v>
       </c>
       <c r="I28" t="n">
-        <v>3786.66</v>
+        <v>3740.34</v>
       </c>
       <c r="J28" t="n">
-        <v>3778.69</v>
+        <v>3872.32</v>
       </c>
       <c r="K28" t="n">
-        <v>3837.78</v>
+        <v>3918.56</v>
       </c>
       <c r="L28" t="n">
-        <v>3896.86</v>
+        <v>3964.79</v>
       </c>
       <c r="M28" t="n">
-        <v>3922.42</v>
+        <v>4053.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3947.98</v>
+        <v>4143</v>
       </c>
       <c r="O28" t="n">
-        <v>4040.59</v>
+        <v>4146.36</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,13 +2873,11 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2902,50 +2892,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3971.2</v>
+        <v>4053.38</v>
       </c>
       <c r="C29" t="n">
-        <v>4058.6</v>
+        <v>4114.84</v>
       </c>
       <c r="D29" t="n">
-        <v>3966.2</v>
+        <v>4051.69</v>
       </c>
       <c r="E29" t="n">
-        <v>4051.43</v>
+        <v>4079.9</v>
       </c>
       <c r="F29" t="n">
-        <v>65.2</v>
+        <v>28.47</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.007</v>
       </c>
       <c r="H29" t="n">
-        <v>92.41</v>
+        <v>63.16</v>
       </c>
       <c r="I29" t="n">
-        <v>3740.34</v>
+        <v>3873.79</v>
       </c>
       <c r="J29" t="n">
-        <v>3872.32</v>
+        <v>3978.53</v>
       </c>
       <c r="K29" t="n">
-        <v>3918.56</v>
+        <v>4005.22</v>
       </c>
       <c r="L29" t="n">
-        <v>3964.79</v>
+        <v>4031.91</v>
       </c>
       <c r="M29" t="n">
-        <v>4053.9</v>
+        <v>4097.63</v>
       </c>
       <c r="N29" t="n">
-        <v>4143</v>
+        <v>4163.34</v>
       </c>
       <c r="O29" t="n">
-        <v>4146.36</v>
+        <v>4151.01</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2982,50 +2972,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4053.38</v>
+        <v>4074.81</v>
       </c>
       <c r="C30" t="n">
-        <v>4114.84</v>
+        <v>4118.75</v>
       </c>
       <c r="D30" t="n">
-        <v>4051.69</v>
+        <v>4061.82</v>
       </c>
       <c r="E30" t="n">
-        <v>4079.9</v>
+        <v>4112.16</v>
       </c>
       <c r="F30" t="n">
-        <v>28.47</v>
+        <v>32.26</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>63.16</v>
+        <v>56.93</v>
       </c>
       <c r="I30" t="n">
-        <v>3873.79</v>
+        <v>3988.53</v>
       </c>
       <c r="J30" t="n">
-        <v>3978.53</v>
+        <v>4015.06</v>
       </c>
       <c r="K30" t="n">
-        <v>4005.22</v>
+        <v>4048.32</v>
       </c>
       <c r="L30" t="n">
-        <v>4031.91</v>
+        <v>4081.58</v>
       </c>
       <c r="M30" t="n">
-        <v>4097.63</v>
+        <v>4111.48</v>
       </c>
       <c r="N30" t="n">
-        <v>4163.34</v>
+        <v>4141.38</v>
       </c>
       <c r="O30" t="n">
-        <v>4151.01</v>
+        <v>4178</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3062,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4074.81</v>
+        <v>4135.45</v>
       </c>
       <c r="C31" t="n">
-        <v>4118.75</v>
+        <v>4183.06</v>
       </c>
       <c r="D31" t="n">
-        <v>4061.82</v>
+        <v>4129.91</v>
       </c>
       <c r="E31" t="n">
-        <v>4112.16</v>
+        <v>4179.95</v>
       </c>
       <c r="F31" t="n">
-        <v>32.26</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H31" t="n">
-        <v>56.93</v>
+        <v>53.15</v>
       </c>
       <c r="I31" t="n">
-        <v>3988.53</v>
+        <v>4004.89</v>
       </c>
       <c r="J31" t="n">
-        <v>4015.06</v>
+        <v>4066.16</v>
       </c>
       <c r="K31" t="n">
-        <v>4048.32</v>
+        <v>4083.69</v>
       </c>
       <c r="L31" t="n">
-        <v>4081.58</v>
+        <v>4101.22</v>
       </c>
       <c r="M31" t="n">
-        <v>4111.48</v>
+        <v>4140.63</v>
       </c>
       <c r="N31" t="n">
-        <v>4141.38</v>
+        <v>4180.03</v>
       </c>
       <c r="O31" t="n">
-        <v>4178</v>
+        <v>4175.69</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3123,14 +3113,18 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3142,63 +3136,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4135.45</v>
+        <v>4201.35</v>
       </c>
       <c r="C32" t="n">
-        <v>4183.06</v>
+        <v>4258.86</v>
       </c>
       <c r="D32" t="n">
-        <v>4129.91</v>
+        <v>4114.08</v>
       </c>
       <c r="E32" t="n">
-        <v>4179.95</v>
+        <v>4135.39</v>
       </c>
       <c r="F32" t="n">
-        <v>67.79000000000001</v>
+        <v>-44.56</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0107</v>
       </c>
       <c r="H32" t="n">
-        <v>53.15</v>
+        <v>144.78</v>
       </c>
       <c r="I32" t="n">
-        <v>4004.89</v>
+        <v>4076.76</v>
       </c>
       <c r="J32" t="n">
-        <v>4066.16</v>
+        <v>4138.53</v>
       </c>
       <c r="K32" t="n">
-        <v>4083.69</v>
+        <v>4153.38</v>
       </c>
       <c r="L32" t="n">
-        <v>4101.22</v>
+        <v>4168.22</v>
       </c>
       <c r="M32" t="n">
-        <v>4140.63</v>
+        <v>4206.53</v>
       </c>
       <c r="N32" t="n">
-        <v>4180.03</v>
+        <v>4244.84</v>
       </c>
       <c r="O32" t="n">
-        <v>4175.69</v>
+        <v>4236.21</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3208,7 +3206,7 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
@@ -3216,152 +3214,142 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4201.35</v>
+        <v>4120.14</v>
       </c>
       <c r="C33" t="n">
-        <v>4258.86</v>
+        <v>4199.53</v>
       </c>
       <c r="D33" t="n">
-        <v>4114.08</v>
+        <v>4067.75</v>
       </c>
       <c r="E33" t="n">
-        <v>4135.39</v>
+        <v>4112.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-44.56</v>
+        <v>-22.49</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.0054</v>
       </c>
       <c r="H33" t="n">
-        <v>144.78</v>
+        <v>131.78</v>
       </c>
       <c r="I33" t="n">
-        <v>4076.76</v>
+        <v>3969.31</v>
       </c>
       <c r="J33" t="n">
-        <v>4138.53</v>
+        <v>3965.07</v>
       </c>
       <c r="K33" t="n">
-        <v>4153.38</v>
+        <v>4063</v>
       </c>
       <c r="L33" t="n">
-        <v>4168.22</v>
+        <v>4160.93</v>
       </c>
       <c r="M33" t="n">
-        <v>4206.53</v>
+        <v>4207.78</v>
       </c>
       <c r="N33" t="n">
-        <v>4244.84</v>
+        <v>4254.62</v>
       </c>
       <c r="O33" t="n">
-        <v>4236.21</v>
+        <v>4403.64</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4120.14</v>
+        <v>4126.34</v>
       </c>
       <c r="C34" t="n">
-        <v>4199.53</v>
+        <v>4153.88</v>
       </c>
       <c r="D34" t="n">
-        <v>4067.75</v>
+        <v>4055.83</v>
       </c>
       <c r="E34" t="n">
-        <v>4112.9</v>
+        <v>4068.57</v>
       </c>
       <c r="F34" t="n">
-        <v>-22.49</v>
+        <v>-44.33</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0108</v>
       </c>
       <c r="H34" t="n">
-        <v>131.78</v>
+        <v>98.05</v>
       </c>
       <c r="I34" t="n">
-        <v>3969.31</v>
+        <v>3935.97</v>
       </c>
       <c r="J34" t="n">
-        <v>3965.07</v>
+        <v>3970.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4063</v>
+        <v>4047.01</v>
       </c>
       <c r="L34" t="n">
-        <v>4160.93</v>
+        <v>4123.27</v>
       </c>
       <c r="M34" t="n">
-        <v>4207.78</v>
+        <v>4178.79</v>
       </c>
       <c r="N34" t="n">
-        <v>4254.62</v>
+        <v>4234.31</v>
       </c>
       <c r="O34" t="n">
-        <v>4403.64</v>
+        <v>4331.31</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,12 +3357,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3396,50 +3386,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4126.34</v>
+        <v>4067.16</v>
       </c>
       <c r="C35" t="n">
-        <v>4153.88</v>
+        <v>4107.05</v>
       </c>
       <c r="D35" t="n">
-        <v>4055.83</v>
+        <v>4015.06</v>
       </c>
       <c r="E35" t="n">
-        <v>4068.57</v>
+        <v>4027.74</v>
       </c>
       <c r="F35" t="n">
-        <v>-44.33</v>
+        <v>-40.83</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.01</v>
       </c>
       <c r="H35" t="n">
-        <v>98.05</v>
+        <v>91.98</v>
       </c>
       <c r="I35" t="n">
-        <v>3935.97</v>
+        <v>3957.77</v>
       </c>
       <c r="J35" t="n">
-        <v>3970.75</v>
+        <v>3952.38</v>
       </c>
       <c r="K35" t="n">
-        <v>4047.01</v>
+        <v>4019.54</v>
       </c>
       <c r="L35" t="n">
-        <v>4123.27</v>
+        <v>4086.71</v>
       </c>
       <c r="M35" t="n">
-        <v>4178.79</v>
+        <v>4117.6</v>
       </c>
       <c r="N35" t="n">
-        <v>4234.31</v>
+        <v>4148.48</v>
       </c>
       <c r="O35" t="n">
-        <v>4331.31</v>
+        <v>4251.93</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3476,50 +3466,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4067.16</v>
+        <v>3938.71</v>
       </c>
       <c r="C36" t="n">
-        <v>4107.05</v>
+        <v>4060.27</v>
       </c>
       <c r="D36" t="n">
-        <v>4015.06</v>
+        <v>3927.85</v>
       </c>
       <c r="E36" t="n">
-        <v>4027.74</v>
+        <v>4031.51</v>
       </c>
       <c r="F36" t="n">
-        <v>-40.83</v>
+        <v>3.78</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>91.98</v>
+        <v>132.42</v>
       </c>
       <c r="I36" t="n">
-        <v>3957.77</v>
+        <v>3923.08</v>
       </c>
       <c r="J36" t="n">
-        <v>3952.38</v>
+        <v>3919.09</v>
       </c>
       <c r="K36" t="n">
-        <v>4019.54</v>
+        <v>3981.74</v>
       </c>
       <c r="L36" t="n">
-        <v>4086.71</v>
+        <v>4044.4</v>
       </c>
       <c r="M36" t="n">
-        <v>4117.6</v>
+        <v>4073.73</v>
       </c>
       <c r="N36" t="n">
-        <v>4148.48</v>
+        <v>4103.06</v>
       </c>
       <c r="O36" t="n">
-        <v>4251.93</v>
+        <v>4199.03</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,12 +3519,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3551,55 +3541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3938.71</v>
+        <v>4053.58</v>
       </c>
       <c r="C37" t="n">
-        <v>4060.27</v>
+        <v>4117.45</v>
       </c>
       <c r="D37" t="n">
-        <v>3927.85</v>
+        <v>4051.06</v>
       </c>
       <c r="E37" t="n">
-        <v>4031.51</v>
+        <v>4090.48</v>
       </c>
       <c r="F37" t="n">
-        <v>3.78</v>
+        <v>58.97</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0146</v>
       </c>
       <c r="H37" t="n">
-        <v>132.42</v>
+        <v>66.39</v>
       </c>
       <c r="I37" t="n">
-        <v>3923.08</v>
+        <v>3795.44</v>
       </c>
       <c r="J37" t="n">
-        <v>3919.09</v>
+        <v>3917.82</v>
       </c>
       <c r="K37" t="n">
-        <v>3981.74</v>
+        <v>3965.3</v>
       </c>
       <c r="L37" t="n">
-        <v>4044.4</v>
+        <v>4012.79</v>
       </c>
       <c r="M37" t="n">
-        <v>4073.73</v>
+        <v>4097.72</v>
       </c>
       <c r="N37" t="n">
-        <v>4103.06</v>
+        <v>4182.66</v>
       </c>
       <c r="O37" t="n">
-        <v>4199.03</v>
+        <v>4192.69</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,18 +3601,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3633,79 +3627,85 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4053.58</v>
+        <v>4093.96</v>
       </c>
       <c r="C38" t="n">
-        <v>4117.45</v>
+        <v>4175.35</v>
       </c>
       <c r="D38" t="n">
-        <v>4051.06</v>
+        <v>4007.86</v>
       </c>
       <c r="E38" t="n">
-        <v>4090.48</v>
+        <v>4027.26</v>
       </c>
       <c r="F38" t="n">
-        <v>58.97</v>
+        <v>-63.22</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0146</v>
+        <v>-0.0155</v>
       </c>
       <c r="H38" t="n">
-        <v>66.39</v>
+        <v>167.49</v>
       </c>
       <c r="I38" t="n">
-        <v>3795.44</v>
+        <v>3984.68</v>
       </c>
       <c r="J38" t="n">
-        <v>3917.82</v>
+        <v>4027.21</v>
       </c>
       <c r="K38" t="n">
-        <v>3965.3</v>
+        <v>4057.29</v>
       </c>
       <c r="L38" t="n">
-        <v>4012.79</v>
+        <v>4087.37</v>
       </c>
       <c r="M38" t="n">
-        <v>4097.72</v>
+        <v>4123.67</v>
       </c>
       <c r="N38" t="n">
-        <v>4182.66</v>
+        <v>4159.98</v>
       </c>
       <c r="O38" t="n">
-        <v>4192.69</v>
+        <v>4183.84</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3717,85 +3717,79 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4093.96</v>
+        <v>4026.69</v>
       </c>
       <c r="C39" t="n">
-        <v>4175.35</v>
+        <v>4143.31</v>
       </c>
       <c r="D39" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E39" t="n">
-        <v>4027.26</v>
+        <v>4043.64</v>
       </c>
       <c r="F39" t="n">
-        <v>-63.22</v>
+        <v>16.38</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0041</v>
       </c>
       <c r="H39" t="n">
-        <v>167.49</v>
+        <v>150.76</v>
       </c>
       <c r="I39" t="n">
-        <v>3984.68</v>
+        <v>3840.37</v>
       </c>
       <c r="J39" t="n">
-        <v>4027.21</v>
+        <v>3827.61</v>
       </c>
       <c r="K39" t="n">
-        <v>4057.29</v>
+        <v>3943.52</v>
       </c>
       <c r="L39" t="n">
-        <v>4087.37</v>
+        <v>4059.43</v>
       </c>
       <c r="M39" t="n">
-        <v>4123.67</v>
+        <v>4111.01</v>
       </c>
       <c r="N39" t="n">
-        <v>4159.98</v>
+        <v>4162.58</v>
       </c>
       <c r="O39" t="n">
-        <v>4183.84</v>
+        <v>4342.84</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3814,50 +3808,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4026.69</v>
+        <v>4059.19</v>
       </c>
       <c r="C40" t="n">
-        <v>4143.31</v>
+        <v>4074.83</v>
       </c>
       <c r="D40" t="n">
-        <v>3992.55</v>
+        <v>3938.88</v>
       </c>
       <c r="E40" t="n">
-        <v>4043.64</v>
+        <v>3996.16</v>
       </c>
       <c r="F40" t="n">
-        <v>16.38</v>
+        <v>-47.48</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0117</v>
       </c>
       <c r="H40" t="n">
-        <v>150.76</v>
+        <v>135.95</v>
       </c>
       <c r="I40" t="n">
-        <v>3840.37</v>
+        <v>3841.79</v>
       </c>
       <c r="J40" t="n">
-        <v>3827.61</v>
+        <v>3880.74</v>
       </c>
       <c r="K40" t="n">
-        <v>3943.52</v>
+        <v>3968.26</v>
       </c>
       <c r="L40" t="n">
-        <v>4059.43</v>
+        <v>4055.79</v>
       </c>
       <c r="M40" t="n">
-        <v>4111.01</v>
+        <v>4119.02</v>
       </c>
       <c r="N40" t="n">
-        <v>4162.58</v>
+        <v>4182.26</v>
       </c>
       <c r="O40" t="n">
-        <v>4342.84</v>
+        <v>4294.07</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3865,18 +3859,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3889,69 +3883,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4059.19</v>
+        <v>3966.02</v>
       </c>
       <c r="C41" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D41" t="n">
-        <v>3938.88</v>
+        <v>3745.17</v>
       </c>
       <c r="E41" t="n">
-        <v>3996.16</v>
+        <v>3764.16</v>
       </c>
       <c r="F41" t="n">
-        <v>-47.48</v>
+        <v>-232.01</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0581</v>
       </c>
       <c r="H41" t="n">
-        <v>135.95</v>
+        <v>237.88</v>
       </c>
       <c r="I41" t="n">
-        <v>3841.79</v>
+        <v>3802.93</v>
       </c>
       <c r="J41" t="n">
-        <v>3880.74</v>
+        <v>3854.87</v>
       </c>
       <c r="K41" t="n">
-        <v>3968.26</v>
+        <v>3928.19</v>
       </c>
       <c r="L41" t="n">
-        <v>4055.79</v>
+        <v>4001.51</v>
       </c>
       <c r="M41" t="n">
-        <v>4119.02</v>
+        <v>4064.14</v>
       </c>
       <c r="N41" t="n">
-        <v>4182.26</v>
+        <v>4126.77</v>
       </c>
       <c r="O41" t="n">
-        <v>4294.07</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>4210.78</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3978,74 +3972,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3966.02</v>
+        <v>3791.66</v>
       </c>
       <c r="C42" t="n">
-        <v>3983.05</v>
+        <v>3884.44</v>
       </c>
       <c r="D42" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E42" t="n">
-        <v>3764.16</v>
+        <v>3814.2</v>
       </c>
       <c r="F42" t="n">
-        <v>-232.01</v>
+        <v>50.04</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0581</v>
+        <v>0.0133</v>
       </c>
       <c r="H42" t="n">
-        <v>237.88</v>
+        <v>143.32</v>
       </c>
       <c r="I42" t="n">
-        <v>3802.93</v>
+        <v>3507.3</v>
       </c>
       <c r="J42" t="n">
-        <v>3854.87</v>
+        <v>3476.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3928.19</v>
+        <v>3645.22</v>
       </c>
       <c r="L42" t="n">
-        <v>4001.51</v>
+        <v>3814.13</v>
       </c>
       <c r="M42" t="n">
-        <v>4064.14</v>
+        <v>3883.09</v>
       </c>
       <c r="N42" t="n">
-        <v>4126.77</v>
+        <v>3952.05</v>
       </c>
       <c r="O42" t="n">
-        <v>4210.78</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>4220.93</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4057,55 +4047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3791.66</v>
+        <v>3808.9</v>
       </c>
       <c r="C43" t="n">
-        <v>3884.44</v>
+        <v>3858.31</v>
       </c>
       <c r="D43" t="n">
-        <v>3741.11</v>
+        <v>3767.5</v>
       </c>
       <c r="E43" t="n">
-        <v>3814.2</v>
+        <v>3832.26</v>
       </c>
       <c r="F43" t="n">
-        <v>50.04</v>
+        <v>18.06</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0047</v>
       </c>
       <c r="H43" t="n">
-        <v>143.32</v>
+        <v>90.81</v>
       </c>
       <c r="I43" t="n">
-        <v>3507.3</v>
+        <v>3597.79</v>
       </c>
       <c r="J43" t="n">
-        <v>3476.3</v>
+        <v>3671.59</v>
       </c>
       <c r="K43" t="n">
-        <v>3645.22</v>
+        <v>3742.54</v>
       </c>
       <c r="L43" t="n">
-        <v>3814.13</v>
+        <v>3813.49</v>
       </c>
       <c r="M43" t="n">
-        <v>3883.09</v>
+        <v>3885.86</v>
       </c>
       <c r="N43" t="n">
-        <v>3952.05</v>
+        <v>3958.24</v>
       </c>
       <c r="O43" t="n">
-        <v>4220.93</v>
+        <v>4027.76</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4121,10 +4115,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4139,57 +4131,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3808.9</v>
+        <v>3812.61</v>
       </c>
       <c r="C44" t="n">
-        <v>3858.31</v>
+        <v>3940.94</v>
       </c>
       <c r="D44" t="n">
-        <v>3767.5</v>
+        <v>3797.64</v>
       </c>
       <c r="E44" t="n">
-        <v>3832.26</v>
+        <v>3940.04</v>
       </c>
       <c r="F44" t="n">
-        <v>18.06</v>
+        <v>107.78</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.0281</v>
       </c>
       <c r="H44" t="n">
-        <v>90.81</v>
+        <v>143.29</v>
       </c>
       <c r="I44" t="n">
-        <v>3597.79</v>
+        <v>3676.7</v>
       </c>
       <c r="J44" t="n">
-        <v>3671.59</v>
+        <v>3751.13</v>
       </c>
       <c r="K44" t="n">
-        <v>3742.54</v>
+        <v>3786.86</v>
       </c>
       <c r="L44" t="n">
-        <v>3813.49</v>
+        <v>3822.58</v>
       </c>
       <c r="M44" t="n">
-        <v>3885.86</v>
+        <v>3877.67</v>
       </c>
       <c r="N44" t="n">
-        <v>3958.24</v>
+        <v>3932.75</v>
       </c>
       <c r="O44" t="n">
-        <v>4027.76</v>
+        <v>3949.12</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,76 +4194,76 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3812.61</v>
+        <v>3943.82</v>
       </c>
       <c r="C45" t="n">
-        <v>3940.94</v>
+        <v>3968.48</v>
       </c>
       <c r="D45" t="n">
-        <v>3797.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E45" t="n">
-        <v>3940.04</v>
+        <v>3927.18</v>
       </c>
       <c r="F45" t="n">
-        <v>107.78</v>
+        <v>-12.86</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0281</v>
+        <v>-0.0033</v>
       </c>
       <c r="H45" t="n">
-        <v>143.29</v>
+        <v>64.77</v>
       </c>
       <c r="I45" t="n">
-        <v>3676.7</v>
+        <v>3654.35</v>
       </c>
       <c r="J45" t="n">
-        <v>3751.13</v>
+        <v>3832.12</v>
       </c>
       <c r="K45" t="n">
-        <v>3786.86</v>
+        <v>3868.39</v>
       </c>
       <c r="L45" t="n">
-        <v>3822.58</v>
+        <v>3904.66</v>
       </c>
       <c r="M45" t="n">
-        <v>3877.67</v>
+        <v>4011.68</v>
       </c>
       <c r="N45" t="n">
-        <v>3932.75</v>
+        <v>4118.7</v>
       </c>
       <c r="O45" t="n">
-        <v>3949.12</v>
+        <v>4084.23</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,18 +4276,14 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4305,55 +4293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3943.82</v>
+        <v>3930.1</v>
       </c>
       <c r="C46" t="n">
-        <v>3968.48</v>
+        <v>3994.18</v>
       </c>
       <c r="D46" t="n">
-        <v>3903.71</v>
+        <v>3879.58</v>
       </c>
       <c r="E46" t="n">
-        <v>3927.18</v>
+        <v>3905.2</v>
       </c>
       <c r="F46" t="n">
-        <v>-12.86</v>
+        <v>-21.97</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0056</v>
       </c>
       <c r="H46" t="n">
-        <v>64.77</v>
+        <v>114.6</v>
       </c>
       <c r="I46" t="n">
-        <v>3654.35</v>
+        <v>3838.93</v>
       </c>
       <c r="J46" t="n">
-        <v>3832.12</v>
+        <v>3857.95</v>
       </c>
       <c r="K46" t="n">
-        <v>3868.39</v>
+        <v>3894.79</v>
       </c>
       <c r="L46" t="n">
-        <v>3904.66</v>
+        <v>3931.63</v>
       </c>
       <c r="M46" t="n">
-        <v>4011.68</v>
+        <v>3959.56</v>
       </c>
       <c r="N46" t="n">
-        <v>4118.7</v>
+        <v>3987.49</v>
       </c>
       <c r="O46" t="n">
-        <v>4084.23</v>
+        <v>4033.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4361,19 +4353,25 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4385,57 +4383,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3930.1</v>
+        <v>3902.7</v>
       </c>
       <c r="C47" t="n">
-        <v>3994.18</v>
+        <v>3970.31</v>
       </c>
       <c r="D47" t="n">
-        <v>3879.58</v>
+        <v>3850.86</v>
       </c>
       <c r="E47" t="n">
-        <v>3905.2</v>
+        <v>3952.18</v>
       </c>
       <c r="F47" t="n">
-        <v>-21.97</v>
+        <v>46.98</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.012</v>
       </c>
       <c r="H47" t="n">
-        <v>114.6</v>
+        <v>119.45</v>
       </c>
       <c r="I47" t="n">
-        <v>3838.93</v>
+        <v>3764.98</v>
       </c>
       <c r="J47" t="n">
-        <v>3857.95</v>
+        <v>3774.76</v>
       </c>
       <c r="K47" t="n">
-        <v>3894.79</v>
+        <v>3847.9</v>
       </c>
       <c r="L47" t="n">
-        <v>3931.63</v>
+        <v>3921.04</v>
       </c>
       <c r="M47" t="n">
-        <v>3959.56</v>
+        <v>3962.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3987.49</v>
+        <v>4003.97</v>
       </c>
       <c r="O47" t="n">
-        <v>4033.25</v>
+        <v>4108.78</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4443,25 +4441,21 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4480,50 +4474,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3902.7</v>
+        <v>3926.53</v>
       </c>
       <c r="C48" t="n">
-        <v>3970.31</v>
+        <v>3995.18</v>
       </c>
       <c r="D48" t="n">
-        <v>3850.86</v>
+        <v>3915.22</v>
       </c>
       <c r="E48" t="n">
-        <v>3952.18</v>
+        <v>3930.12</v>
       </c>
       <c r="F48" t="n">
-        <v>46.98</v>
+        <v>-22.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0056</v>
       </c>
       <c r="H48" t="n">
-        <v>119.45</v>
+        <v>79.95</v>
       </c>
       <c r="I48" t="n">
-        <v>3764.98</v>
+        <v>3731.42</v>
       </c>
       <c r="J48" t="n">
-        <v>3774.76</v>
+        <v>3853.53</v>
       </c>
       <c r="K48" t="n">
-        <v>3847.9</v>
+        <v>3892.46</v>
       </c>
       <c r="L48" t="n">
-        <v>3921.04</v>
+        <v>3931.38</v>
       </c>
       <c r="M48" t="n">
-        <v>3962.5</v>
+        <v>4011.9</v>
       </c>
       <c r="N48" t="n">
-        <v>4003.97</v>
+        <v>4092.42</v>
       </c>
       <c r="O48" t="n">
-        <v>4108.78</v>
+        <v>4089.76</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,15 +4528,13 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4557,57 +4549,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3926.53</v>
+        <v>3942.51</v>
       </c>
       <c r="C49" t="n">
-        <v>3995.18</v>
+        <v>3958.12</v>
       </c>
       <c r="D49" t="n">
-        <v>3915.22</v>
+        <v>3852.03</v>
       </c>
       <c r="E49" t="n">
-        <v>3930.12</v>
+        <v>3888.11</v>
       </c>
       <c r="F49" t="n">
-        <v>-22.06</v>
+        <v>-42</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0107</v>
       </c>
       <c r="H49" t="n">
-        <v>79.95</v>
+        <v>106.08</v>
       </c>
       <c r="I49" t="n">
-        <v>3731.42</v>
+        <v>3835.27</v>
       </c>
       <c r="J49" t="n">
-        <v>3853.53</v>
+        <v>3837.62</v>
       </c>
       <c r="K49" t="n">
-        <v>3892.46</v>
+        <v>3890.14</v>
       </c>
       <c r="L49" t="n">
-        <v>3931.38</v>
+        <v>3942.66</v>
       </c>
       <c r="M49" t="n">
-        <v>4011.9</v>
+        <v>3970.09</v>
       </c>
       <c r="N49" t="n">
-        <v>4092.42</v>
+        <v>3997.53</v>
       </c>
       <c r="O49" t="n">
-        <v>4089.76</v>
+        <v>4075.13</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,12 +4607,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4639,57 +4633,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3942.51</v>
+        <v>3867.02</v>
       </c>
       <c r="C50" t="n">
-        <v>3958.12</v>
+        <v>3919.67</v>
       </c>
       <c r="D50" t="n">
-        <v>3852.03</v>
+        <v>3842.72</v>
       </c>
       <c r="E50" t="n">
-        <v>3888.11</v>
+        <v>3911.87</v>
       </c>
       <c r="F50" t="n">
-        <v>-42</v>
+        <v>23.76</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H50" t="n">
-        <v>106.08</v>
+        <v>76.95</v>
       </c>
       <c r="I50" t="n">
-        <v>3835.27</v>
+        <v>3745.95</v>
       </c>
       <c r="J50" t="n">
-        <v>3837.62</v>
+        <v>3773.54</v>
       </c>
       <c r="K50" t="n">
-        <v>3890.14</v>
+        <v>3835.07</v>
       </c>
       <c r="L50" t="n">
-        <v>3942.66</v>
+        <v>3896.59</v>
       </c>
       <c r="M50" t="n">
-        <v>3970.09</v>
+        <v>3941.15</v>
       </c>
       <c r="N50" t="n">
-        <v>3997.53</v>
+        <v>3985.71</v>
       </c>
       <c r="O50" t="n">
-        <v>4075.13</v>
+        <v>4064.2</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4697,14 +4691,12 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4723,57 +4715,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3867.02</v>
+        <v>3920.27</v>
       </c>
       <c r="C51" t="n">
-        <v>3919.67</v>
+        <v>3967.68</v>
       </c>
       <c r="D51" t="n">
-        <v>3842.72</v>
+        <v>3888.37</v>
       </c>
       <c r="E51" t="n">
-        <v>3911.87</v>
+        <v>3888.37</v>
       </c>
       <c r="F51" t="n">
-        <v>23.76</v>
+        <v>-23.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="H51" t="n">
-        <v>76.95</v>
+        <v>79.31</v>
       </c>
       <c r="I51" t="n">
-        <v>3745.95</v>
+        <v>3765.77</v>
       </c>
       <c r="J51" t="n">
-        <v>3773.54</v>
+        <v>3850.26</v>
       </c>
       <c r="K51" t="n">
-        <v>3835.07</v>
+        <v>3873.4</v>
       </c>
       <c r="L51" t="n">
-        <v>3896.59</v>
+        <v>3896.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3941.15</v>
+        <v>3950.35</v>
       </c>
       <c r="N51" t="n">
-        <v>3985.71</v>
+        <v>4004.16</v>
       </c>
       <c r="O51" t="n">
-        <v>4064.2</v>
+        <v>3996.62</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4784,13 +4776,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4805,76 +4799,78 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3920.27</v>
+        <v>3878.41</v>
       </c>
       <c r="C52" t="n">
-        <v>3967.68</v>
+        <v>3878.41</v>
       </c>
       <c r="D52" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E52" t="n">
-        <v>3888.37</v>
+        <v>3842.2</v>
       </c>
       <c r="F52" t="n">
-        <v>-23.5</v>
+        <v>-46.18</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0119</v>
       </c>
       <c r="H52" t="n">
-        <v>79.31</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>3765.77</v>
+        <v>3809.07</v>
       </c>
       <c r="J52" t="n">
-        <v>3850.26</v>
+        <v>3789.24</v>
       </c>
       <c r="K52" t="n">
-        <v>3873.4</v>
+        <v>3848.72</v>
       </c>
       <c r="L52" t="n">
-        <v>3896.53</v>
+        <v>3908.2</v>
       </c>
       <c r="M52" t="n">
-        <v>3950.35</v>
+        <v>3928.03</v>
       </c>
       <c r="N52" t="n">
-        <v>4004.16</v>
+        <v>3947.85</v>
       </c>
       <c r="O52" t="n">
-        <v>3996.62</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
+        <v>4046.99</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4889,65 +4885,65 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3878.41</v>
+        <v>3838.98</v>
       </c>
       <c r="C53" t="n">
-        <v>3878.41</v>
+        <v>3864.12</v>
       </c>
       <c r="D53" t="n">
-        <v>3806.67</v>
+        <v>3754.14</v>
       </c>
       <c r="E53" t="n">
-        <v>3842.2</v>
+        <v>3813.79</v>
       </c>
       <c r="F53" t="n">
-        <v>-46.18</v>
+        <v>-28.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0074</v>
       </c>
       <c r="H53" t="n">
-        <v>71.73999999999999</v>
+        <v>109.98</v>
       </c>
       <c r="I53" t="n">
-        <v>3809.07</v>
+        <v>3734.93</v>
       </c>
       <c r="J53" t="n">
-        <v>3789.24</v>
+        <v>3770.28</v>
       </c>
       <c r="K53" t="n">
-        <v>3848.72</v>
+        <v>3806.33</v>
       </c>
       <c r="L53" t="n">
-        <v>3908.2</v>
+        <v>3842.37</v>
       </c>
       <c r="M53" t="n">
-        <v>3928.03</v>
+        <v>3878.06</v>
       </c>
       <c r="N53" t="n">
-        <v>3947.85</v>
+        <v>3913.76</v>
       </c>
       <c r="O53" t="n">
-        <v>4046.99</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>3950.15</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4982,62 +4978,62 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3838.98</v>
+        <v>3806.98</v>
       </c>
       <c r="C54" t="n">
-        <v>3864.12</v>
+        <v>3828.22</v>
       </c>
       <c r="D54" t="n">
-        <v>3754.14</v>
+        <v>3674.82</v>
       </c>
       <c r="E54" t="n">
-        <v>3813.79</v>
+        <v>3716.28</v>
       </c>
       <c r="F54" t="n">
-        <v>-28.4</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0256</v>
       </c>
       <c r="H54" t="n">
-        <v>109.98</v>
+        <v>153.4</v>
       </c>
       <c r="I54" t="n">
-        <v>3734.93</v>
+        <v>3644.15</v>
       </c>
       <c r="J54" t="n">
-        <v>3770.28</v>
+        <v>3706.14</v>
       </c>
       <c r="K54" t="n">
-        <v>3806.33</v>
+        <v>3758.8</v>
       </c>
       <c r="L54" t="n">
-        <v>3842.37</v>
+        <v>3811.46</v>
       </c>
       <c r="M54" t="n">
-        <v>3878.06</v>
+        <v>3868.78</v>
       </c>
       <c r="N54" t="n">
-        <v>3913.76</v>
+        <v>3926.11</v>
       </c>
       <c r="O54" t="n">
-        <v>3950.15</v>
+        <v>3974.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5068,58 +5064,56 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3806.98</v>
+        <v>3694.12</v>
       </c>
       <c r="C55" t="n">
-        <v>3828.22</v>
+        <v>3743.8</v>
       </c>
       <c r="D55" t="n">
-        <v>3674.82</v>
+        <v>3574.27</v>
       </c>
       <c r="E55" t="n">
-        <v>3716.28</v>
+        <v>3690.48</v>
       </c>
       <c r="F55" t="n">
-        <v>-97.51000000000001</v>
+        <v>-25.81</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.0069</v>
       </c>
       <c r="H55" t="n">
-        <v>153.4</v>
+        <v>169.53</v>
       </c>
       <c r="I55" t="n">
-        <v>3644.15</v>
+        <v>3521.42</v>
       </c>
       <c r="J55" t="n">
-        <v>3706.14</v>
+        <v>3545.27</v>
       </c>
       <c r="K55" t="n">
-        <v>3758.8</v>
+        <v>3639.58</v>
       </c>
       <c r="L55" t="n">
-        <v>3811.46</v>
+        <v>3733.9</v>
       </c>
       <c r="M55" t="n">
-        <v>3868.78</v>
+        <v>3792.98</v>
       </c>
       <c r="N55" t="n">
-        <v>3926.11</v>
+        <v>3852.07</v>
       </c>
       <c r="O55" t="n">
-        <v>3974.1</v>
+        <v>3981.62</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5128,7 +5122,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5154,50 +5148,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3694.12</v>
+        <v>3671</v>
       </c>
       <c r="C56" t="n">
-        <v>3743.8</v>
+        <v>3708.2</v>
       </c>
       <c r="D56" t="n">
-        <v>3574.27</v>
+        <v>3595.26</v>
       </c>
       <c r="E56" t="n">
-        <v>3690.48</v>
+        <v>3599.02</v>
       </c>
       <c r="F56" t="n">
-        <v>-25.81</v>
+        <v>-91.45999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0069</v>
+        <v>-0.0248</v>
       </c>
       <c r="H56" t="n">
-        <v>169.53</v>
+        <v>112.94</v>
       </c>
       <c r="I56" t="n">
-        <v>3521.42</v>
+        <v>3404.74</v>
       </c>
       <c r="J56" t="n">
-        <v>3545.27</v>
+        <v>3536.67</v>
       </c>
       <c r="K56" t="n">
-        <v>3639.58</v>
+        <v>3605.71</v>
       </c>
       <c r="L56" t="n">
-        <v>3733.9</v>
+        <v>3674.76</v>
       </c>
       <c r="M56" t="n">
-        <v>3792.98</v>
+        <v>3775.24</v>
       </c>
       <c r="N56" t="n">
-        <v>3852.07</v>
+        <v>3875.72</v>
       </c>
       <c r="O56" t="n">
-        <v>3981.62</v>
+        <v>3913.33</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5207,12 +5201,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5230,88 +5224,6 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3671</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3708.2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3645.26</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3651.43</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-39.04</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="H57" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3404.74</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3536.67</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3605.71</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3674.76</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3775.24</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3875.72</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3913.33</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>
